--- a/myprojects/ExelProj/Data Cleaning_AI.xlsx
+++ b/myprojects/ExelProj/Data Cleaning_AI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inanj\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inanj\Documents\GitHub\inakm.github.io\myprojects\ExelProj\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCEB7E5E-5D68-4B11-921E-F7ECD6D1B608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D69A4544-69B1-4AA2-B8BE-4C0B3334F7AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" activeTab="1" xr2:uid="{6A5DF63E-A673-4076-95D6-237D43ABA7F8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{6A5DF63E-A673-4076-95D6-237D43ABA7F8}"/>
   </bookViews>
   <sheets>
     <sheet name="OLD Data" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -990,7 +990,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1009,8 +1009,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1018,18 +1024,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1379,11 +1408,11 @@
     <col min="8" max="8" width="1.44140625" style="1" customWidth="1"/>
     <col min="10" max="11" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="35.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="35.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.21875" customWidth="1"/>
+    <col min="15" max="15" width="9.77734375" customWidth="1"/>
     <col min="16" max="16" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -1408,34 +1437,34 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="8" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1461,23 +1490,23 @@
       <c r="G2" t="s">
         <v>13</v>
       </c>
-      <c r="I2" t="str">
+      <c r="I2" s="4" t="str">
         <f>A2</f>
         <v>C001</v>
       </c>
-      <c r="J2" t="str">
+      <c r="J2" s="4" t="str">
         <f>LEFT(B2, FIND(" ", B2) - 1)</f>
         <v>Pooja</v>
       </c>
-      <c r="K2" t="str">
+      <c r="K2" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B2, " "), {"#",";","_","-"})</f>
         <v>Kumar</v>
       </c>
-      <c r="L2" t="str" cm="1">
+      <c r="L2" s="4" t="str" cm="1">
         <f t="array" ref="L2">LEFT(_xlfn.CONCAT(IFERROR(MID(B2, _xlfn.SEQUENCE(LEN(B2)), 1) + 0, "")), 10)</f>
         <v>1000000001</v>
       </c>
-      <c r="M2" t="str" cm="1">
+      <c r="M2" s="6" t="str" cm="1">
         <f t="array" ref="M2">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C2, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -1488,7 +1517,7 @@
 )</f>
         <v>poojakumar1000000001@gmail.com</v>
       </c>
-      <c r="N2" t="str" cm="1">
+      <c r="N2" s="4" t="str" cm="1">
         <f t="array" ref="N2:O2">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D2, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -1498,10 +1527,10 @@
 )</f>
         <v>Chennai</v>
       </c>
-      <c r="O2" t="str">
+      <c r="O2" s="4" t="str">
         <v>600674</v>
       </c>
-      <c r="P2" s="3" cm="1">
+      <c r="P2" s="5" cm="1">
         <f t="array" ref="P2">_xlfn.LET(
     _xlpm.val, TRIM(E2),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -1520,11 +1549,11 @@
 )</f>
         <v>45669</v>
       </c>
-      <c r="Q2" t="str" cm="1">
+      <c r="Q2" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q2" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F2, ROW(INDIRECT("1:" &amp; LEN(F2))), 1) * 1, ""))</f>
         <v>56906</v>
       </c>
-      <c r="R2" t="str" cm="1">
+      <c r="R2" s="4" t="str" cm="1">
         <f t="array" ref="R2">TRIM(_xlfn.REDUCE(G2, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>call later</v>
       </c>
@@ -1551,23 +1580,23 @@
       <c r="G3" t="s">
         <v>13</v>
       </c>
-      <c r="I3" t="str">
-        <f t="shared" ref="I3:I53" si="0">A3</f>
+      <c r="I3" s="4" t="str">
+        <f t="shared" ref="I3:I51" si="0">A3</f>
         <v>C002</v>
       </c>
-      <c r="J3" t="str">
+      <c r="J3" s="4" t="str">
         <f t="shared" ref="J3:J51" si="1">LEFT(B3, FIND(" ", B3) - 1)</f>
         <v>Vikram</v>
       </c>
-      <c r="K3" t="str">
+      <c r="K3" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B3, " "), {"#",";","_","-"})</f>
         <v>Saxena</v>
       </c>
-      <c r="L3" t="str" cm="1">
+      <c r="L3" s="4" t="str" cm="1">
         <f t="array" ref="L3">LEFT(_xlfn.CONCAT(IFERROR(MID(B3, _xlfn.SEQUENCE(LEN(B3)), 1) + 0, "")), 10)</f>
         <v>1000000002</v>
       </c>
-      <c r="M3" t="str" cm="1">
+      <c r="M3" s="6" t="str" cm="1">
         <f t="array" ref="M3">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C3, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -1578,7 +1607,7 @@
 )</f>
         <v>vikramsaxena1000000002@gmail.com</v>
       </c>
-      <c r="N3" t="str" cm="1">
+      <c r="N3" s="4" t="str" cm="1">
         <f t="array" ref="N3:O3">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D3, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -1588,10 +1617,10 @@
 )</f>
         <v>Chennai</v>
       </c>
-      <c r="O3" t="str">
+      <c r="O3" s="4" t="str">
         <v>600332</v>
       </c>
-      <c r="P3" s="3" cm="1">
+      <c r="P3" s="5" cm="1">
         <f t="array" ref="P3">_xlfn.LET(
     _xlpm.val, TRIM(E3),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -1610,11 +1639,11 @@
 )</f>
         <v>45676</v>
       </c>
-      <c r="Q3" t="str" cm="1">
+      <c r="Q3" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q3" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F3, ROW(INDIRECT("1:" &amp; LEN(F3))), 1) * 1, ""))</f>
         <v>86483</v>
       </c>
-      <c r="R3" t="str" cm="1">
+      <c r="R3" s="4" t="str" cm="1">
         <f t="array" ref="R3">TRIM(_xlfn.REDUCE(G3, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>call later</v>
       </c>
@@ -1641,23 +1670,23 @@
       <c r="G4" t="s">
         <v>26</v>
       </c>
-      <c r="I4" t="str">
+      <c r="I4" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C003</v>
       </c>
-      <c r="J4" t="str">
+      <c r="J4" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pallavi</v>
       </c>
-      <c r="K4" t="str">
+      <c r="K4" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B4, " "), {"#",";","_","-"})</f>
         <v>Dubey</v>
       </c>
-      <c r="L4" t="str" cm="1">
+      <c r="L4" s="4" t="str" cm="1">
         <f t="array" ref="L4">LEFT(_xlfn.CONCAT(IFERROR(MID(B4, _xlfn.SEQUENCE(LEN(B4)), 1) + 0, "")), 10)</f>
         <v>1000000003</v>
       </c>
-      <c r="M4" t="str" cm="1">
+      <c r="M4" s="6" t="str" cm="1">
         <f t="array" ref="M4">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C4, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -1668,7 +1697,7 @@
 )</f>
         <v>pallavidubey1000000003@gmail.com</v>
       </c>
-      <c r="N4" t="str" cm="1">
+      <c r="N4" s="4" t="str" cm="1">
         <f t="array" ref="N4:O4">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D4, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -1678,10 +1707,10 @@
 )</f>
         <v>Bangalore</v>
       </c>
-      <c r="O4" t="str">
+      <c r="O4" s="4" t="str">
         <v>560559</v>
       </c>
-      <c r="P4" s="3" cm="1">
+      <c r="P4" s="5" cm="1">
         <f t="array" ref="P4">_xlfn.LET(
     _xlpm.val, TRIM(E4),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -1700,11 +1729,11 @@
 )</f>
         <v>45664</v>
       </c>
-      <c r="Q4" t="str" cm="1">
+      <c r="Q4" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q4" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F4, ROW(INDIRECT("1:" &amp; LEN(F4))), 1) * 1, ""))</f>
         <v>66757</v>
       </c>
-      <c r="R4" t="str" cm="1">
+      <c r="R4" s="4" t="str" cm="1">
         <f t="array" ref="R4">TRIM(_xlfn.REDUCE(G4, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>followuphigh</v>
       </c>
@@ -1731,23 +1760,23 @@
       <c r="G5" t="s">
         <v>33</v>
       </c>
-      <c r="I5" t="str">
+      <c r="I5" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C004</v>
       </c>
-      <c r="J5" t="str">
+      <c r="J5" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Krishna</v>
       </c>
-      <c r="K5" t="str">
+      <c r="K5" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B5, " "), {"#",";","_","-"})</f>
         <v>Trivedi</v>
       </c>
-      <c r="L5" t="str" cm="1">
+      <c r="L5" s="4" t="str" cm="1">
         <f t="array" ref="L5">LEFT(_xlfn.CONCAT(IFERROR(MID(B5, _xlfn.SEQUENCE(LEN(B5)), 1) + 0, "")), 10)</f>
         <v>1000000004</v>
       </c>
-      <c r="M5" t="str" cm="1">
+      <c r="M5" s="6" t="str" cm="1">
         <f t="array" ref="M5">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C5, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -1758,7 +1787,7 @@
 )</f>
         <v>krishnatrivedi1000000004@gmail.com</v>
       </c>
-      <c r="N5" t="str" cm="1">
+      <c r="N5" s="4" t="str" cm="1">
         <f t="array" ref="N5:O5">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D5, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -1768,10 +1797,10 @@
 )</f>
         <v>Bangalore</v>
       </c>
-      <c r="O5" t="str">
+      <c r="O5" s="4" t="str">
         <v>560595</v>
       </c>
-      <c r="P5" s="3" cm="1">
+      <c r="P5" s="5" cm="1">
         <f t="array" ref="P5">_xlfn.LET(
     _xlpm.val, TRIM(E5),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -1790,11 +1819,11 @@
 )</f>
         <v>45664</v>
       </c>
-      <c r="Q5" t="str" cm="1">
+      <c r="Q5" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q5" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F5, ROW(INDIRECT("1:" &amp; LEN(F5))), 1) * 1, ""))</f>
         <v>52781</v>
       </c>
-      <c r="R5" t="str" cm="1">
+      <c r="R5" s="4" t="str" cm="1">
         <f t="array" ref="R5">TRIM(_xlfn.REDUCE(G5, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>VIP client</v>
       </c>
@@ -1821,23 +1850,23 @@
       <c r="G6" t="s">
         <v>40</v>
       </c>
-      <c r="I6" t="str">
+      <c r="I6" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C005</v>
       </c>
-      <c r="J6" t="str">
+      <c r="J6" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kavya</v>
       </c>
-      <c r="K6" t="str">
+      <c r="K6" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B6, " "), {"#",";","_","-"})</f>
         <v>Ghosh</v>
       </c>
-      <c r="L6" t="str" cm="1">
+      <c r="L6" s="4" t="str" cm="1">
         <f t="array" ref="L6">LEFT(_xlfn.CONCAT(IFERROR(MID(B6, _xlfn.SEQUENCE(LEN(B6)), 1) + 0, "")), 10)</f>
         <v>1000000005</v>
       </c>
-      <c r="M6" t="str" cm="1">
+      <c r="M6" s="6" t="str" cm="1">
         <f t="array" ref="M6">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C6, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -1848,7 +1877,7 @@
 )</f>
         <v>kavyaghosh1000000005@outlook.com</v>
       </c>
-      <c r="N6" t="str" cm="1">
+      <c r="N6" s="4" t="str" cm="1">
         <f t="array" ref="N6:O6">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D6, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -1858,10 +1887,10 @@
 )</f>
         <v>Bangalore</v>
       </c>
-      <c r="O6" t="str">
+      <c r="O6" s="4" t="str">
         <v>560045</v>
       </c>
-      <c r="P6" s="3" cm="1">
+      <c r="P6" s="5" cm="1">
         <f t="array" ref="P6">_xlfn.LET(
     _xlpm.val, TRIM(E6),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -1880,11 +1909,11 @@
 )</f>
         <v>45675</v>
       </c>
-      <c r="Q6" t="str" cm="1">
+      <c r="Q6" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q6" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F6, ROW(INDIRECT("1:" &amp; LEN(F6))), 1) * 1, ""))</f>
         <v>67416</v>
       </c>
-      <c r="R6" t="str" cm="1">
+      <c r="R6" s="4" t="str" cm="1">
         <f t="array" ref="R6">TRIM(_xlfn.REDUCE(G6, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>urgent</v>
       </c>
@@ -1911,23 +1940,23 @@
       <c r="G7" t="s">
         <v>47</v>
       </c>
-      <c r="I7" t="str">
+      <c r="I7" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C006</v>
       </c>
-      <c r="J7" t="str">
+      <c r="J7" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Vikram</v>
       </c>
-      <c r="K7" t="str">
+      <c r="K7" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B7, " "), {"#",";","_","-"})</f>
         <v>Joshi</v>
       </c>
-      <c r="L7" t="str" cm="1">
+      <c r="L7" s="4" t="str" cm="1">
         <f t="array" ref="L7">LEFT(_xlfn.CONCAT(IFERROR(MID(B7, _xlfn.SEQUENCE(LEN(B7)), 1) + 0, "")), 10)</f>
         <v>1000000006</v>
       </c>
-      <c r="M7" t="str" cm="1">
+      <c r="M7" s="6" t="str" cm="1">
         <f t="array" ref="M7">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C7, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -1938,7 +1967,7 @@
 )</f>
         <v>vikramjoshi1000000006@yahoo.com</v>
       </c>
-      <c r="N7" t="str" cm="1">
+      <c r="N7" s="4" t="str" cm="1">
         <f t="array" ref="N7:O7">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D7, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -1948,10 +1977,10 @@
 )</f>
         <v>Delhi</v>
       </c>
-      <c r="O7" t="str">
+      <c r="O7" s="4" t="str">
         <v>110928</v>
       </c>
-      <c r="P7" s="3" cm="1">
+      <c r="P7" s="5" cm="1">
         <f t="array" ref="P7">_xlfn.LET(
     _xlpm.val, TRIM(E7),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -1970,11 +1999,11 @@
 )</f>
         <v>45661</v>
       </c>
-      <c r="Q7" t="str" cm="1">
+      <c r="Q7" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q7" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F7, ROW(INDIRECT("1:" &amp; LEN(F7))), 1) * 1, ""))</f>
         <v>15383</v>
       </c>
-      <c r="R7" t="str" cm="1">
+      <c r="R7" s="4" t="str" cm="1">
         <f t="array" ref="R7">TRIM(_xlfn.REDUCE(G7, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>pending</v>
       </c>
@@ -2001,23 +2030,23 @@
       <c r="G8" t="s">
         <v>33</v>
       </c>
-      <c r="I8" t="str">
+      <c r="I8" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C007</v>
       </c>
-      <c r="J8" t="str">
+      <c r="J8" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Sai</v>
       </c>
-      <c r="K8" t="str">
+      <c r="K8" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B8, " "), {"#",";","_","-"})</f>
         <v>Kumar</v>
       </c>
-      <c r="L8" t="str" cm="1">
+      <c r="L8" s="4" t="str" cm="1">
         <f t="array" ref="L8">LEFT(_xlfn.CONCAT(IFERROR(MID(B8, _xlfn.SEQUENCE(LEN(B8)), 1) + 0, "")), 10)</f>
         <v>1000000007</v>
       </c>
-      <c r="M8" t="str" cm="1">
+      <c r="M8" s="6" t="str" cm="1">
         <f t="array" ref="M8">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C8, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -2028,7 +2057,7 @@
 )</f>
         <v>saikumar1000000007@gmail.com</v>
       </c>
-      <c r="N8" t="str" cm="1">
+      <c r="N8" s="4" t="str" cm="1">
         <f t="array" ref="N8:O8">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D8, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -2038,10 +2067,10 @@
 )</f>
         <v>Hyderabad</v>
       </c>
-      <c r="O8" t="str">
+      <c r="O8" s="4" t="str">
         <v>500929</v>
       </c>
-      <c r="P8" s="3" cm="1">
+      <c r="P8" s="5" cm="1">
         <f t="array" ref="P8">_xlfn.LET(
     _xlpm.val, TRIM(E8),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -2060,11 +2089,11 @@
 )</f>
         <v>45673</v>
       </c>
-      <c r="Q8" t="str" cm="1">
+      <c r="Q8" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q8" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F8, ROW(INDIRECT("1:" &amp; LEN(F8))), 1) * 1, ""))</f>
         <v>98580</v>
       </c>
-      <c r="R8" t="str" cm="1">
+      <c r="R8" s="4" t="str" cm="1">
         <f t="array" ref="R8">TRIM(_xlfn.REDUCE(G8, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>VIP client</v>
       </c>
@@ -2091,23 +2120,23 @@
       <c r="G9" t="s">
         <v>47</v>
       </c>
-      <c r="I9" t="str">
+      <c r="I9" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C008</v>
       </c>
-      <c r="J9" t="str">
+      <c r="J9" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Rohan</v>
       </c>
-      <c r="K9" t="str">
+      <c r="K9" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B9, " "), {"#",";","_","-"})</f>
         <v>Sharma</v>
       </c>
-      <c r="L9" t="str" cm="1">
+      <c r="L9" s="4" t="str" cm="1">
         <f t="array" ref="L9">LEFT(_xlfn.CONCAT(IFERROR(MID(B9, _xlfn.SEQUENCE(LEN(B9)), 1) + 0, "")), 10)</f>
         <v>1000000008</v>
       </c>
-      <c r="M9" t="str" cm="1">
+      <c r="M9" s="6" t="str" cm="1">
         <f t="array" ref="M9">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C9, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -2118,7 +2147,7 @@
 )</f>
         <v>rohansharma1000000008@outlook.com</v>
       </c>
-      <c r="N9" t="str" cm="1">
+      <c r="N9" s="4" t="str" cm="1">
         <f t="array" ref="N9:O9">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D9, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -2128,10 +2157,10 @@
 )</f>
         <v>Mumbai</v>
       </c>
-      <c r="O9" t="str">
+      <c r="O9" s="4" t="str">
         <v>400209</v>
       </c>
-      <c r="P9" s="3" cm="1">
+      <c r="P9" s="5" cm="1">
         <f t="array" ref="P9">_xlfn.LET(
     _xlpm.val, TRIM(E9),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -2150,11 +2179,11 @@
 )</f>
         <v>45684</v>
       </c>
-      <c r="Q9" t="str" cm="1">
+      <c r="Q9" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q9" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F9, ROW(INDIRECT("1:" &amp; LEN(F9))), 1) * 1, ""))</f>
         <v>61329</v>
       </c>
-      <c r="R9" t="str" cm="1">
+      <c r="R9" s="4" t="str" cm="1">
         <f t="array" ref="R9">TRIM(_xlfn.REDUCE(G9, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>pending</v>
       </c>
@@ -2181,23 +2210,23 @@
       <c r="G10" t="s">
         <v>26</v>
       </c>
-      <c r="I10" t="str">
+      <c r="I10" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C009</v>
       </c>
-      <c r="J10" t="str">
+      <c r="J10" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Aditi</v>
       </c>
-      <c r="K10" t="str">
+      <c r="K10" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B10, " "), {"#",";","_","-"})</f>
         <v>Kumar</v>
       </c>
-      <c r="L10" t="str" cm="1">
+      <c r="L10" s="4" t="str" cm="1">
         <f t="array" ref="L10">LEFT(_xlfn.CONCAT(IFERROR(MID(B10, _xlfn.SEQUENCE(LEN(B10)), 1) + 0, "")), 10)</f>
         <v>1000000009</v>
       </c>
-      <c r="M10" t="str" cm="1">
+      <c r="M10" s="6" t="str" cm="1">
         <f t="array" ref="M10">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C10, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -2208,7 +2237,7 @@
 )</f>
         <v>aditikumar1000000009@outlook.com</v>
       </c>
-      <c r="N10" t="str" cm="1">
+      <c r="N10" s="4" t="str" cm="1">
         <f t="array" ref="N10:O10">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D10, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -2218,10 +2247,10 @@
 )</f>
         <v>Hyderabad</v>
       </c>
-      <c r="O10" t="str">
+      <c r="O10" s="4" t="str">
         <v>500725</v>
       </c>
-      <c r="P10" s="3" cm="1">
+      <c r="P10" s="5" cm="1">
         <f t="array" ref="P10">_xlfn.LET(
     _xlpm.val, TRIM(E10),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -2240,11 +2269,11 @@
 )</f>
         <v>45667</v>
       </c>
-      <c r="Q10" t="str" cm="1">
+      <c r="Q10" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q10" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F10, ROW(INDIRECT("1:" &amp; LEN(F10))), 1) * 1, ""))</f>
         <v>34319</v>
       </c>
-      <c r="R10" t="str" cm="1">
+      <c r="R10" s="4" t="str" cm="1">
         <f t="array" ref="R10">TRIM(_xlfn.REDUCE(G10, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>followuphigh</v>
       </c>
@@ -2271,23 +2300,23 @@
       <c r="G11" t="s">
         <v>33</v>
       </c>
-      <c r="I11" t="str">
+      <c r="I11" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C010</v>
       </c>
-      <c r="J11" t="str">
+      <c r="J11" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Vihaan</v>
       </c>
-      <c r="K11" t="str">
+      <c r="K11" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B11, " "), {"#",";","_","-"})</f>
         <v>Saxena</v>
       </c>
-      <c r="L11" t="str" cm="1">
+      <c r="L11" s="4" t="str" cm="1">
         <f t="array" ref="L11">LEFT(_xlfn.CONCAT(IFERROR(MID(B11, _xlfn.SEQUENCE(LEN(B11)), 1) + 0, "")), 10)</f>
         <v>1000000010</v>
       </c>
-      <c r="M11" t="str" cm="1">
+      <c r="M11" s="6" t="str" cm="1">
         <f t="array" ref="M11">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C11, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -2298,7 +2327,7 @@
 )</f>
         <v>vihaansaxena1000000010@yahoo.com</v>
       </c>
-      <c r="N11" t="str" cm="1">
+      <c r="N11" s="4" t="str" cm="1">
         <f t="array" ref="N11:O11">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D11, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -2308,10 +2337,10 @@
 )</f>
         <v>Bangalore</v>
       </c>
-      <c r="O11" t="str">
+      <c r="O11" s="4" t="str">
         <v>560940</v>
       </c>
-      <c r="P11" s="3" cm="1">
+      <c r="P11" s="5" cm="1">
         <f t="array" ref="P11">_xlfn.LET(
     _xlpm.val, TRIM(E11),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -2330,11 +2359,11 @@
 )</f>
         <v>45662</v>
       </c>
-      <c r="Q11" t="str" cm="1">
+      <c r="Q11" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q11" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F11, ROW(INDIRECT("1:" &amp; LEN(F11))), 1) * 1, ""))</f>
         <v>67850</v>
       </c>
-      <c r="R11" t="str" cm="1">
+      <c r="R11" s="4" t="str" cm="1">
         <f t="array" ref="R11">TRIM(_xlfn.REDUCE(G11, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>VIP client</v>
       </c>
@@ -2361,23 +2390,23 @@
       <c r="G12" t="s">
         <v>33</v>
       </c>
-      <c r="I12" t="str">
+      <c r="I12" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C011</v>
       </c>
-      <c r="J12" t="str">
+      <c r="J12" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pooja</v>
       </c>
-      <c r="K12" t="str">
+      <c r="K12" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B12, " "), {"#",";","_","-"})</f>
         <v>Kumar</v>
       </c>
-      <c r="L12" t="str" cm="1">
+      <c r="L12" s="4" t="str" cm="1">
         <f t="array" ref="L12">LEFT(_xlfn.CONCAT(IFERROR(MID(B12, _xlfn.SEQUENCE(LEN(B12)), 1) + 0, "")), 10)</f>
         <v>1000000011</v>
       </c>
-      <c r="M12" t="str" cm="1">
+      <c r="M12" s="6" t="str" cm="1">
         <f t="array" ref="M12">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C12, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -2388,7 +2417,7 @@
 )</f>
         <v>poojakumar1000000011@gmail.com</v>
       </c>
-      <c r="N12" t="str" cm="1">
+      <c r="N12" s="4" t="str" cm="1">
         <f t="array" ref="N12:O12">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D12, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -2398,10 +2427,10 @@
 )</f>
         <v>Chennai</v>
       </c>
-      <c r="O12" t="str">
+      <c r="O12" s="4" t="str">
         <v>600883</v>
       </c>
-      <c r="P12" s="3" cm="1">
+      <c r="P12" s="5" cm="1">
         <f t="array" ref="P12">_xlfn.LET(
     _xlpm.val, TRIM(E12),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -2420,11 +2449,11 @@
 )</f>
         <v>45666</v>
       </c>
-      <c r="Q12" t="str" cm="1">
+      <c r="Q12" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q12" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F12, ROW(INDIRECT("1:" &amp; LEN(F12))), 1) * 1, ""))</f>
         <v>34366</v>
       </c>
-      <c r="R12" t="str" cm="1">
+      <c r="R12" s="4" t="str" cm="1">
         <f t="array" ref="R12">TRIM(_xlfn.REDUCE(G12, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>VIP client</v>
       </c>
@@ -2451,23 +2480,23 @@
       <c r="G13" t="s">
         <v>40</v>
       </c>
-      <c r="I13" t="str">
+      <c r="I13" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C012</v>
       </c>
-      <c r="J13" t="str">
+      <c r="J13" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Vikram</v>
       </c>
-      <c r="K13" t="str">
+      <c r="K13" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B13, " "), {"#",";","_","-"})</f>
         <v>Saxena</v>
       </c>
-      <c r="L13" t="str" cm="1">
+      <c r="L13" s="4" t="str" cm="1">
         <f t="array" ref="L13">LEFT(_xlfn.CONCAT(IFERROR(MID(B13, _xlfn.SEQUENCE(LEN(B13)), 1) + 0, "")), 10)</f>
         <v>1000000012</v>
       </c>
-      <c r="M13" t="str" cm="1">
+      <c r="M13" s="6" t="str" cm="1">
         <f t="array" ref="M13">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C13, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -2478,7 +2507,7 @@
 )</f>
         <v>vikramsaxena1000000012@gmail.com</v>
       </c>
-      <c r="N13" t="str" cm="1">
+      <c r="N13" s="4" t="str" cm="1">
         <f t="array" ref="N13:O13">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D13, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -2488,10 +2517,10 @@
 )</f>
         <v>Delhi</v>
       </c>
-      <c r="O13" t="str">
+      <c r="O13" s="4" t="str">
         <v>110689</v>
       </c>
-      <c r="P13" s="3" cm="1">
+      <c r="P13" s="5" cm="1">
         <f t="array" ref="P13">_xlfn.LET(
     _xlpm.val, TRIM(E13),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -2510,11 +2539,11 @@
 )</f>
         <v>45685</v>
       </c>
-      <c r="Q13" t="str" cm="1">
+      <c r="Q13" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q13" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F13, ROW(INDIRECT("1:" &amp; LEN(F13))), 1) * 1, ""))</f>
         <v>6557</v>
       </c>
-      <c r="R13" t="str" cm="1">
+      <c r="R13" s="4" t="str" cm="1">
         <f t="array" ref="R13">TRIM(_xlfn.REDUCE(G13, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>urgent</v>
       </c>
@@ -2541,23 +2570,23 @@
       <c r="G14" t="s">
         <v>90</v>
       </c>
-      <c r="I14" t="str">
+      <c r="I14" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C013</v>
       </c>
-      <c r="J14" t="str">
+      <c r="J14" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pallavi</v>
       </c>
-      <c r="K14" t="str">
+      <c r="K14" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B14, " "), {"#",";","_","-"})</f>
         <v>Dubey</v>
       </c>
-      <c r="L14" t="str" cm="1">
+      <c r="L14" s="4" t="str" cm="1">
         <f t="array" ref="L14">LEFT(_xlfn.CONCAT(IFERROR(MID(B14, _xlfn.SEQUENCE(LEN(B14)), 1) + 0, "")), 10)</f>
         <v>1000000013</v>
       </c>
-      <c r="M14" t="str" cm="1">
+      <c r="M14" s="6" t="str" cm="1">
         <f t="array" ref="M14">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C14, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -2568,7 +2597,7 @@
 )</f>
         <v>pallavidubey1000000013@gmail.com</v>
       </c>
-      <c r="N14" t="str" cm="1">
+      <c r="N14" s="4" t="str" cm="1">
         <f t="array" ref="N14:O14">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D14, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -2578,10 +2607,10 @@
 )</f>
         <v>Pune</v>
       </c>
-      <c r="O14" t="str">
+      <c r="O14" s="4" t="str">
         <v>411529</v>
       </c>
-      <c r="P14" s="3" cm="1">
+      <c r="P14" s="5" cm="1">
         <f t="array" ref="P14">_xlfn.LET(
     _xlpm.val, TRIM(E14),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -2600,11 +2629,11 @@
 )</f>
         <v>45666</v>
       </c>
-      <c r="Q14" t="str" cm="1">
+      <c r="Q14" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q14" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F14, ROW(INDIRECT("1:" &amp; LEN(F14))), 1) * 1, ""))</f>
         <v>69930</v>
       </c>
-      <c r="R14" t="str" cm="1">
+      <c r="R14" s="4" t="str" cm="1">
         <f t="array" ref="R14">TRIM(_xlfn.REDUCE(G14, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>new lead</v>
       </c>
@@ -2631,23 +2660,23 @@
       <c r="G15" t="s">
         <v>13</v>
       </c>
-      <c r="I15" t="str">
+      <c r="I15" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C014</v>
       </c>
-      <c r="J15" t="str">
+      <c r="J15" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Krishna</v>
       </c>
-      <c r="K15" t="str">
+      <c r="K15" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B15, " "), {"#",";","_","-"})</f>
         <v>Trivedi</v>
       </c>
-      <c r="L15" t="str" cm="1">
+      <c r="L15" s="4" t="str" cm="1">
         <f t="array" ref="L15">LEFT(_xlfn.CONCAT(IFERROR(MID(B15, _xlfn.SEQUENCE(LEN(B15)), 1) + 0, "")), 10)</f>
         <v>1000000014</v>
       </c>
-      <c r="M15" t="str" cm="1">
+      <c r="M15" s="6" t="str" cm="1">
         <f t="array" ref="M15">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C15, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -2658,7 +2687,7 @@
 )</f>
         <v>krishnatrivedi1000000014@gmail.com</v>
       </c>
-      <c r="N15" t="str" cm="1">
+      <c r="N15" s="4" t="str" cm="1">
         <f t="array" ref="N15:O15">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D15, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -2668,10 +2697,10 @@
 )</f>
         <v>Bangalore</v>
       </c>
-      <c r="O15" t="str">
+      <c r="O15" s="4" t="str">
         <v>560059</v>
       </c>
-      <c r="P15" s="3" cm="1">
+      <c r="P15" s="5" cm="1">
         <f t="array" ref="P15">_xlfn.LET(
     _xlpm.val, TRIM(E15),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -2690,11 +2719,11 @@
 )</f>
         <v>45685</v>
       </c>
-      <c r="Q15" t="str" cm="1">
+      <c r="Q15" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q15" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F15, ROW(INDIRECT("1:" &amp; LEN(F15))), 1) * 1, ""))</f>
         <v>36723</v>
       </c>
-      <c r="R15" t="str" cm="1">
+      <c r="R15" s="4" t="str" cm="1">
         <f t="array" ref="R15">TRIM(_xlfn.REDUCE(G15, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>call later</v>
       </c>
@@ -2721,23 +2750,23 @@
       <c r="G16" t="s">
         <v>13</v>
       </c>
-      <c r="I16" t="str">
+      <c r="I16" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C015</v>
       </c>
-      <c r="J16" t="str">
+      <c r="J16" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kavya</v>
       </c>
-      <c r="K16" t="str">
+      <c r="K16" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B16, " "), {"#",";","_","-"})</f>
         <v>Ghosh</v>
       </c>
-      <c r="L16" t="str" cm="1">
+      <c r="L16" s="4" t="str" cm="1">
         <f t="array" ref="L16">LEFT(_xlfn.CONCAT(IFERROR(MID(B16, _xlfn.SEQUENCE(LEN(B16)), 1) + 0, "")), 10)</f>
         <v>1000000015</v>
       </c>
-      <c r="M16" t="str" cm="1">
+      <c r="M16" s="6" t="str" cm="1">
         <f t="array" ref="M16">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C16, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -2748,7 +2777,7 @@
 )</f>
         <v>kavyaghosh1000000015@outlook.com</v>
       </c>
-      <c r="N16" t="str" cm="1">
+      <c r="N16" s="4" t="str" cm="1">
         <f t="array" ref="N16:O16">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D16, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -2758,10 +2787,10 @@
 )</f>
         <v>Mumbai</v>
       </c>
-      <c r="O16" t="str">
+      <c r="O16" s="4" t="str">
         <v>400574</v>
       </c>
-      <c r="P16" s="3" cm="1">
+      <c r="P16" s="5" cm="1">
         <f t="array" ref="P16">_xlfn.LET(
     _xlpm.val, TRIM(E16),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -2780,11 +2809,11 @@
 )</f>
         <v>45659</v>
       </c>
-      <c r="Q16" t="str" cm="1">
+      <c r="Q16" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q16" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F16, ROW(INDIRECT("1:" &amp; LEN(F16))), 1) * 1, ""))</f>
         <v>92799</v>
       </c>
-      <c r="R16" t="str" cm="1">
+      <c r="R16" s="4" t="str" cm="1">
         <f t="array" ref="R16">TRIM(_xlfn.REDUCE(G16, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>call later</v>
       </c>
@@ -2811,23 +2840,23 @@
       <c r="G17" t="s">
         <v>26</v>
       </c>
-      <c r="I17" t="str">
+      <c r="I17" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C016</v>
       </c>
-      <c r="J17" t="str">
+      <c r="J17" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Vikram</v>
       </c>
-      <c r="K17" t="str">
+      <c r="K17" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B17, " "), {"#",";","_","-"})</f>
         <v>Joshi</v>
       </c>
-      <c r="L17" t="str" cm="1">
+      <c r="L17" s="4" t="str" cm="1">
         <f t="array" ref="L17">LEFT(_xlfn.CONCAT(IFERROR(MID(B17, _xlfn.SEQUENCE(LEN(B17)), 1) + 0, "")), 10)</f>
         <v>1000000016</v>
       </c>
-      <c r="M17" t="str" cm="1">
+      <c r="M17" s="6" t="str" cm="1">
         <f t="array" ref="M17">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C17, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -2838,7 +2867,7 @@
 )</f>
         <v>vikramjoshi1000000016@yahoo.com</v>
       </c>
-      <c r="N17" t="str" cm="1">
+      <c r="N17" s="4" t="str" cm="1">
         <f t="array" ref="N17:O17">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D17, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -2848,10 +2877,10 @@
 )</f>
         <v>Bangalore</v>
       </c>
-      <c r="O17" t="str">
+      <c r="O17" s="4" t="str">
         <v>560201</v>
       </c>
-      <c r="P17" s="3" cm="1">
+      <c r="P17" s="5" cm="1">
         <f t="array" ref="P17">_xlfn.LET(
     _xlpm.val, TRIM(E17),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -2870,11 +2899,11 @@
 )</f>
         <v>45670</v>
       </c>
-      <c r="Q17" t="str" cm="1">
+      <c r="Q17" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q17" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F17, ROW(INDIRECT("1:" &amp; LEN(F17))), 1) * 1, ""))</f>
         <v>94896</v>
       </c>
-      <c r="R17" t="str" cm="1">
+      <c r="R17" s="4" t="str" cm="1">
         <f t="array" ref="R17">TRIM(_xlfn.REDUCE(G17, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>followuphigh</v>
       </c>
@@ -2901,23 +2930,23 @@
       <c r="G18" t="s">
         <v>40</v>
       </c>
-      <c r="I18" t="str">
+      <c r="I18" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C017</v>
       </c>
-      <c r="J18" t="str">
+      <c r="J18" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Sai</v>
       </c>
-      <c r="K18" t="str">
+      <c r="K18" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B18, " "), {"#",";","_","-"})</f>
         <v>Kumar</v>
       </c>
-      <c r="L18" t="str" cm="1">
+      <c r="L18" s="4" t="str" cm="1">
         <f t="array" ref="L18">LEFT(_xlfn.CONCAT(IFERROR(MID(B18, _xlfn.SEQUENCE(LEN(B18)), 1) + 0, "")), 10)</f>
         <v>1000000017</v>
       </c>
-      <c r="M18" t="str" cm="1">
+      <c r="M18" s="6" t="str" cm="1">
         <f t="array" ref="M18">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C18, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -2928,7 +2957,7 @@
 )</f>
         <v>saikumar1000000017@gmail.com</v>
       </c>
-      <c r="N18" t="str" cm="1">
+      <c r="N18" s="4" t="str" cm="1">
         <f t="array" ref="N18:O18">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D18, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -2938,10 +2967,10 @@
 )</f>
         <v>Chennai</v>
       </c>
-      <c r="O18" t="str">
+      <c r="O18" s="4" t="str">
         <v>600667</v>
       </c>
-      <c r="P18" s="3" cm="1">
+      <c r="P18" s="5" cm="1">
         <f t="array" ref="P18">_xlfn.LET(
     _xlpm.val, TRIM(E18),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -2960,11 +2989,11 @@
 )</f>
         <v>45663</v>
       </c>
-      <c r="Q18" t="str" cm="1">
+      <c r="Q18" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q18" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F18, ROW(INDIRECT("1:" &amp; LEN(F18))), 1) * 1, ""))</f>
         <v>55501</v>
       </c>
-      <c r="R18" t="str" cm="1">
+      <c r="R18" s="4" t="str" cm="1">
         <f t="array" ref="R18">TRIM(_xlfn.REDUCE(G18, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>urgent</v>
       </c>
@@ -2991,23 +3020,23 @@
       <c r="G19" t="s">
         <v>33</v>
       </c>
-      <c r="I19" t="str">
+      <c r="I19" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C018</v>
       </c>
-      <c r="J19" t="str">
+      <c r="J19" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Rohan</v>
       </c>
-      <c r="K19" t="str">
+      <c r="K19" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B19, " "), {"#",";","_","-"})</f>
         <v>Sharma</v>
       </c>
-      <c r="L19" t="str" cm="1">
+      <c r="L19" s="4" t="str" cm="1">
         <f t="array" ref="L19">LEFT(_xlfn.CONCAT(IFERROR(MID(B19, _xlfn.SEQUENCE(LEN(B19)), 1) + 0, "")), 10)</f>
         <v>1000000018</v>
       </c>
-      <c r="M19" t="str" cm="1">
+      <c r="M19" s="6" t="str" cm="1">
         <f t="array" ref="M19">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C19, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -3018,7 +3047,7 @@
 )</f>
         <v>rohansharma1000000018@outlook.com</v>
       </c>
-      <c r="N19" t="str" cm="1">
+      <c r="N19" s="4" t="str" cm="1">
         <f t="array" ref="N19:O19">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D19, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -3028,10 +3057,10 @@
 )</f>
         <v>Bangalore</v>
       </c>
-      <c r="O19" t="str">
+      <c r="O19" s="4" t="str">
         <v>560156</v>
       </c>
-      <c r="P19" s="3" cm="1">
+      <c r="P19" s="5" cm="1">
         <f t="array" ref="P19">_xlfn.LET(
     _xlpm.val, TRIM(E19),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -3050,11 +3079,11 @@
 )</f>
         <v>45668</v>
       </c>
-      <c r="Q19" t="str" cm="1">
+      <c r="Q19" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q19" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F19, ROW(INDIRECT("1:" &amp; LEN(F19))), 1) * 1, ""))</f>
         <v>74583</v>
       </c>
-      <c r="R19" t="str" cm="1">
+      <c r="R19" s="4" t="str" cm="1">
         <f t="array" ref="R19">TRIM(_xlfn.REDUCE(G19, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>VIP client</v>
       </c>
@@ -3081,23 +3110,23 @@
       <c r="G20" t="s">
         <v>90</v>
       </c>
-      <c r="I20" t="str">
+      <c r="I20" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C019</v>
       </c>
-      <c r="J20" t="str">
+      <c r="J20" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Aditi</v>
       </c>
-      <c r="K20" t="str">
+      <c r="K20" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B20, " "), {"#",";","_","-"})</f>
         <v>Kumar</v>
       </c>
-      <c r="L20" t="str" cm="1">
+      <c r="L20" s="4" t="str" cm="1">
         <f t="array" ref="L20">LEFT(_xlfn.CONCAT(IFERROR(MID(B20, _xlfn.SEQUENCE(LEN(B20)), 1) + 0, "")), 10)</f>
         <v>1000000019</v>
       </c>
-      <c r="M20" t="str" cm="1">
+      <c r="M20" s="6" t="str" cm="1">
         <f t="array" ref="M20">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C20, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -3108,7 +3137,7 @@
 )</f>
         <v>aditikumar1000000019@outlook.com</v>
       </c>
-      <c r="N20" t="str" cm="1">
+      <c r="N20" s="4" t="str" cm="1">
         <f t="array" ref="N20:O20">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D20, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -3118,10 +3147,10 @@
 )</f>
         <v>Bangalore</v>
       </c>
-      <c r="O20" t="str">
+      <c r="O20" s="4" t="str">
         <v>560586</v>
       </c>
-      <c r="P20" s="3" cm="1">
+      <c r="P20" s="5" cm="1">
         <f t="array" ref="P20">_xlfn.LET(
     _xlpm.val, TRIM(E20),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -3140,11 +3169,11 @@
 )</f>
         <v>45661</v>
       </c>
-      <c r="Q20" t="str" cm="1">
+      <c r="Q20" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q20" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F20, ROW(INDIRECT("1:" &amp; LEN(F20))), 1) * 1, ""))</f>
         <v>92974</v>
       </c>
-      <c r="R20" t="str" cm="1">
+      <c r="R20" s="4" t="str" cm="1">
         <f t="array" ref="R20">TRIM(_xlfn.REDUCE(G20, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>new lead</v>
       </c>
@@ -3171,23 +3200,23 @@
       <c r="G21" t="s">
         <v>33</v>
       </c>
-      <c r="I21" t="str">
+      <c r="I21" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C020</v>
       </c>
-      <c r="J21" t="str">
+      <c r="J21" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Vihaan</v>
       </c>
-      <c r="K21" t="str">
+      <c r="K21" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B21, " "), {"#",";","_","-"})</f>
         <v>Saxena</v>
       </c>
-      <c r="L21" t="str" cm="1">
+      <c r="L21" s="4" t="str" cm="1">
         <f t="array" ref="L21">LEFT(_xlfn.CONCAT(IFERROR(MID(B21, _xlfn.SEQUENCE(LEN(B21)), 1) + 0, "")), 10)</f>
         <v>1000000020</v>
       </c>
-      <c r="M21" t="str" cm="1">
+      <c r="M21" s="6" t="str" cm="1">
         <f t="array" ref="M21">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C21, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -3198,7 +3227,7 @@
 )</f>
         <v>vihaansaxena1000000020@yahoo.com</v>
       </c>
-      <c r="N21" t="str" cm="1">
+      <c r="N21" s="4" t="str" cm="1">
         <f t="array" ref="N21:O21">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D21, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -3208,10 +3237,10 @@
 )</f>
         <v>Hyderabad</v>
       </c>
-      <c r="O21" t="str">
+      <c r="O21" s="4" t="str">
         <v>500706</v>
       </c>
-      <c r="P21" s="3" cm="1">
+      <c r="P21" s="5" cm="1">
         <f t="array" ref="P21">_xlfn.LET(
     _xlpm.val, TRIM(E21),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -3230,11 +3259,11 @@
 )</f>
         <v>45682</v>
       </c>
-      <c r="Q21" t="str" cm="1">
+      <c r="Q21" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q21" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F21, ROW(INDIRECT("1:" &amp; LEN(F21))), 1) * 1, ""))</f>
         <v>30298</v>
       </c>
-      <c r="R21" t="str" cm="1">
+      <c r="R21" s="4" t="str" cm="1">
         <f t="array" ref="R21">TRIM(_xlfn.REDUCE(G21, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>VIP client</v>
       </c>
@@ -3261,23 +3290,23 @@
       <c r="G22" t="s">
         <v>13</v>
       </c>
-      <c r="I22" t="str">
+      <c r="I22" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C021</v>
       </c>
-      <c r="J22" t="str">
+      <c r="J22" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pooja</v>
       </c>
-      <c r="K22" t="str">
+      <c r="K22" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B22, " "), {"#",";","_","-"})</f>
         <v>Kumar</v>
       </c>
-      <c r="L22" t="str" cm="1">
+      <c r="L22" s="4" t="str" cm="1">
         <f t="array" ref="L22">LEFT(_xlfn.CONCAT(IFERROR(MID(B22, _xlfn.SEQUENCE(LEN(B22)), 1) + 0, "")), 10)</f>
         <v>1000000021</v>
       </c>
-      <c r="M22" t="str" cm="1">
+      <c r="M22" s="6" t="str" cm="1">
         <f t="array" ref="M22">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C22, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -3288,7 +3317,7 @@
 )</f>
         <v>poojakumar1000000021@gmail.com</v>
       </c>
-      <c r="N22" t="str" cm="1">
+      <c r="N22" s="4" t="str" cm="1">
         <f t="array" ref="N22:O22">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D22, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -3298,10 +3327,10 @@
 )</f>
         <v>Pune</v>
       </c>
-      <c r="O22" t="str">
+      <c r="O22" s="4" t="str">
         <v>411481</v>
       </c>
-      <c r="P22" s="3" cm="1">
+      <c r="P22" s="5" cm="1">
         <f t="array" ref="P22">_xlfn.LET(
     _xlpm.val, TRIM(E22),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -3320,11 +3349,11 @@
 )</f>
         <v>45672</v>
       </c>
-      <c r="Q22" t="str" cm="1">
+      <c r="Q22" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q22" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F22, ROW(INDIRECT("1:" &amp; LEN(F22))), 1) * 1, ""))</f>
         <v>31131</v>
       </c>
-      <c r="R22" t="str" cm="1">
+      <c r="R22" s="4" t="str" cm="1">
         <f t="array" ref="R22">TRIM(_xlfn.REDUCE(G22, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>call later</v>
       </c>
@@ -3351,23 +3380,23 @@
       <c r="G23" t="s">
         <v>47</v>
       </c>
-      <c r="I23" t="str">
+      <c r="I23" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C022</v>
       </c>
-      <c r="J23" t="str">
+      <c r="J23" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Vikram</v>
       </c>
-      <c r="K23" t="str">
+      <c r="K23" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B23, " "), {"#",";","_","-"})</f>
         <v>Saxena</v>
       </c>
-      <c r="L23" t="str" cm="1">
+      <c r="L23" s="4" t="str" cm="1">
         <f t="array" ref="L23">LEFT(_xlfn.CONCAT(IFERROR(MID(B23, _xlfn.SEQUENCE(LEN(B23)), 1) + 0, "")), 10)</f>
         <v>1000000022</v>
       </c>
-      <c r="M23" t="str" cm="1">
+      <c r="M23" s="6" t="str" cm="1">
         <f t="array" ref="M23">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C23, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -3378,7 +3407,7 @@
 )</f>
         <v>vikramsaxena1000000022@gmail.com</v>
       </c>
-      <c r="N23" t="str" cm="1">
+      <c r="N23" s="4" t="str" cm="1">
         <f t="array" ref="N23:O23">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D23, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -3388,10 +3417,10 @@
 )</f>
         <v>Hyderabad</v>
       </c>
-      <c r="O23" t="str">
+      <c r="O23" s="4" t="str">
         <v>500047</v>
       </c>
-      <c r="P23" s="3" cm="1">
+      <c r="P23" s="5" cm="1">
         <f t="array" ref="P23">_xlfn.LET(
     _xlpm.val, TRIM(E23),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -3410,11 +3439,11 @@
 )</f>
         <v>45669</v>
       </c>
-      <c r="Q23" t="str" cm="1">
+      <c r="Q23" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q23" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F23, ROW(INDIRECT("1:" &amp; LEN(F23))), 1) * 1, ""))</f>
         <v>76114</v>
       </c>
-      <c r="R23" t="str" cm="1">
+      <c r="R23" s="4" t="str" cm="1">
         <f t="array" ref="R23">TRIM(_xlfn.REDUCE(G23, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>pending</v>
       </c>
@@ -3441,23 +3470,23 @@
       <c r="G24" t="s">
         <v>47</v>
       </c>
-      <c r="I24" t="str">
+      <c r="I24" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C023</v>
       </c>
-      <c r="J24" t="str">
+      <c r="J24" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pallavi</v>
       </c>
-      <c r="K24" t="str">
+      <c r="K24" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B24, " "), {"#",";","_","-"})</f>
         <v>Dubey</v>
       </c>
-      <c r="L24" t="str" cm="1">
+      <c r="L24" s="4" t="str" cm="1">
         <f t="array" ref="L24">LEFT(_xlfn.CONCAT(IFERROR(MID(B24, _xlfn.SEQUENCE(LEN(B24)), 1) + 0, "")), 10)</f>
         <v>1000000023</v>
       </c>
-      <c r="M24" t="str" cm="1">
+      <c r="M24" s="6" t="str" cm="1">
         <f t="array" ref="M24">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C24, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -3468,7 +3497,7 @@
 )</f>
         <v>pallavidubey1000000023@gmail.com</v>
       </c>
-      <c r="N24" t="str" cm="1">
+      <c r="N24" s="4" t="str" cm="1">
         <f t="array" ref="N24:O24">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D24, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -3478,10 +3507,10 @@
 )</f>
         <v>Bangalore</v>
       </c>
-      <c r="O24" t="str">
+      <c r="O24" s="4" t="str">
         <v>560572</v>
       </c>
-      <c r="P24" s="3" cm="1">
+      <c r="P24" s="5" cm="1">
         <f t="array" ref="P24">_xlfn.LET(
     _xlpm.val, TRIM(E24),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -3500,11 +3529,11 @@
 )</f>
         <v>45676</v>
       </c>
-      <c r="Q24" t="str" cm="1">
+      <c r="Q24" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q24" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F24, ROW(INDIRECT("1:" &amp; LEN(F24))), 1) * 1, ""))</f>
         <v>65983</v>
       </c>
-      <c r="R24" t="str" cm="1">
+      <c r="R24" s="4" t="str" cm="1">
         <f t="array" ref="R24">TRIM(_xlfn.REDUCE(G24, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>pending</v>
       </c>
@@ -3531,23 +3560,23 @@
       <c r="G25" t="s">
         <v>47</v>
       </c>
-      <c r="I25" t="str">
+      <c r="I25" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C024</v>
       </c>
-      <c r="J25" t="str">
+      <c r="J25" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Krishna</v>
       </c>
-      <c r="K25" t="str">
+      <c r="K25" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B25, " "), {"#",";","_","-"})</f>
         <v>Trivedi</v>
       </c>
-      <c r="L25" t="str" cm="1">
+      <c r="L25" s="4" t="str" cm="1">
         <f t="array" ref="L25">LEFT(_xlfn.CONCAT(IFERROR(MID(B25, _xlfn.SEQUENCE(LEN(B25)), 1) + 0, "")), 10)</f>
         <v>1000000024</v>
       </c>
-      <c r="M25" t="str" cm="1">
+      <c r="M25" s="6" t="str" cm="1">
         <f t="array" ref="M25">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C25, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -3558,7 +3587,7 @@
 )</f>
         <v>krishnatrivedi1000000024@gmail.com</v>
       </c>
-      <c r="N25" t="str" cm="1">
+      <c r="N25" s="4" t="str" cm="1">
         <f t="array" ref="N25:O25">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D25, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -3568,10 +3597,10 @@
 )</f>
         <v>Pune</v>
       </c>
-      <c r="O25" t="str">
+      <c r="O25" s="4" t="str">
         <v>411206</v>
       </c>
-      <c r="P25" s="3" cm="1">
+      <c r="P25" s="5" cm="1">
         <f t="array" ref="P25">_xlfn.LET(
     _xlpm.val, TRIM(E25),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -3590,11 +3619,11 @@
 )</f>
         <v>45681</v>
       </c>
-      <c r="Q25" t="str" cm="1">
+      <c r="Q25" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q25" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F25, ROW(INDIRECT("1:" &amp; LEN(F25))), 1) * 1, ""))</f>
         <v>45343</v>
       </c>
-      <c r="R25" t="str" cm="1">
+      <c r="R25" s="4" t="str" cm="1">
         <f t="array" ref="R25">TRIM(_xlfn.REDUCE(G25, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>pending</v>
       </c>
@@ -3621,23 +3650,23 @@
       <c r="G26" t="s">
         <v>13</v>
       </c>
-      <c r="I26" t="str">
+      <c r="I26" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C025</v>
       </c>
-      <c r="J26" t="str">
+      <c r="J26" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Aarav</v>
       </c>
-      <c r="K26" t="str">
+      <c r="K26" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B26, " "), {"#",";","_","-"})</f>
         <v>Mehta</v>
       </c>
-      <c r="L26" t="str" cm="1">
+      <c r="L26" s="4" t="str" cm="1">
         <f t="array" ref="L26">LEFT(_xlfn.CONCAT(IFERROR(MID(B26, _xlfn.SEQUENCE(LEN(B26)), 1) + 0, "")), 10)</f>
         <v>1000000025</v>
       </c>
-      <c r="M26" t="str" cm="1">
+      <c r="M26" s="6" t="str" cm="1">
         <f t="array" ref="M26">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C26, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -3648,7 +3677,7 @@
 )</f>
         <v>aaravmehta1000000025@gmail.com</v>
       </c>
-      <c r="N26" t="str" cm="1">
+      <c r="N26" s="4" t="str" cm="1">
         <f t="array" ref="N26:O26">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D26, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -3658,10 +3687,10 @@
 )</f>
         <v>Chennai</v>
       </c>
-      <c r="O26" t="str">
+      <c r="O26" s="4" t="str">
         <v>500025</v>
       </c>
-      <c r="P26" s="3" cm="1">
+      <c r="P26" s="5" cm="1">
         <f t="array" ref="P26">_xlfn.LET(
     _xlpm.val, TRIM(E26),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -3680,11 +3709,11 @@
 )</f>
         <v>45658</v>
       </c>
-      <c r="Q26" t="str" cm="1">
+      <c r="Q26" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q26" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F26, ROW(INDIRECT("1:" &amp; LEN(F26))), 1) * 1, ""))</f>
         <v>50025</v>
       </c>
-      <c r="R26" t="str" cm="1">
+      <c r="R26" s="4" t="str" cm="1">
         <f t="array" ref="R26">TRIM(_xlfn.REDUCE(G26, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>call later</v>
       </c>
@@ -3711,23 +3740,23 @@
       <c r="G27" t="s">
         <v>33</v>
       </c>
-      <c r="I27" t="str">
+      <c r="I27" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C026</v>
       </c>
-      <c r="J27" t="str">
+      <c r="J27" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Diya</v>
       </c>
-      <c r="K27" t="str">
+      <c r="K27" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B27, " "), {"#",";","_","-"})</f>
         <v>Sharma</v>
       </c>
-      <c r="L27" t="str" cm="1">
+      <c r="L27" s="4" t="str" cm="1">
         <f t="array" ref="L27">LEFT(_xlfn.CONCAT(IFERROR(MID(B27, _xlfn.SEQUENCE(LEN(B27)), 1) + 0, "")), 10)</f>
         <v>1000000026</v>
       </c>
-      <c r="M27" t="str" cm="1">
+      <c r="M27" s="6" t="str" cm="1">
         <f t="array" ref="M27">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C27, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -3738,7 +3767,7 @@
 )</f>
         <v>diyasharma1000000026@gmail.com</v>
       </c>
-      <c r="N27" t="str" cm="1">
+      <c r="N27" s="4" t="str" cm="1">
         <f t="array" ref="N27:O27">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D27, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -3748,10 +3777,10 @@
 )</f>
         <v>Bangalore</v>
       </c>
-      <c r="O27" t="str">
+      <c r="O27" s="4" t="str">
         <v>500026</v>
       </c>
-      <c r="P27" s="3" cm="1">
+      <c r="P27" s="5" cm="1">
         <f t="array" ref="P27">_xlfn.LET(
     _xlpm.val, TRIM(E27),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -3770,11 +3799,11 @@
 )</f>
         <v>45659</v>
       </c>
-      <c r="Q27" t="str" cm="1">
+      <c r="Q27" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q27" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F27, ROW(INDIRECT("1:" &amp; LEN(F27))), 1) * 1, ""))</f>
         <v>50026</v>
       </c>
-      <c r="R27" t="str" cm="1">
+      <c r="R27" s="4" t="str" cm="1">
         <f t="array" ref="R27">TRIM(_xlfn.REDUCE(G27, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>VIP client</v>
       </c>
@@ -3801,23 +3830,23 @@
       <c r="G28" t="s">
         <v>47</v>
       </c>
-      <c r="I28" t="str">
+      <c r="I28" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C027</v>
       </c>
-      <c r="J28" t="str">
+      <c r="J28" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kabir</v>
       </c>
-      <c r="K28" t="str">
+      <c r="K28" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B28, " "), {"#",";","_","-"})</f>
         <v>Verma</v>
       </c>
-      <c r="L28" t="str" cm="1">
+      <c r="L28" s="4" t="str" cm="1">
         <f t="array" ref="L28">LEFT(_xlfn.CONCAT(IFERROR(MID(B28, _xlfn.SEQUENCE(LEN(B28)), 1) + 0, "")), 10)</f>
         <v>1000000027</v>
       </c>
-      <c r="M28" t="str" cm="1">
+      <c r="M28" s="6" t="str" cm="1">
         <f t="array" ref="M28">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C28, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -3828,7 +3857,7 @@
 )</f>
         <v>kabirverma1000000027@gmail.com</v>
       </c>
-      <c r="N28" t="str" cm="1">
+      <c r="N28" s="4" t="str" cm="1">
         <f t="array" ref="N28:O28">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D28, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -3838,10 +3867,10 @@
 )</f>
         <v>Hyderabad</v>
       </c>
-      <c r="O28" t="str">
+      <c r="O28" s="4" t="str">
         <v>500027</v>
       </c>
-      <c r="P28" s="3" cm="1">
+      <c r="P28" s="5" cm="1">
         <f t="array" ref="P28">_xlfn.LET(
     _xlpm.val, TRIM(E28),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -3860,11 +3889,11 @@
 )</f>
         <v>45660</v>
       </c>
-      <c r="Q28" t="str" cm="1">
+      <c r="Q28" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q28" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F28, ROW(INDIRECT("1:" &amp; LEN(F28))), 1) * 1, ""))</f>
         <v>50027</v>
       </c>
-      <c r="R28" t="str" cm="1">
+      <c r="R28" s="4" t="str" cm="1">
         <f t="array" ref="R28">TRIM(_xlfn.REDUCE(G28, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>pending</v>
       </c>
@@ -3891,23 +3920,23 @@
       <c r="G29" t="s">
         <v>26</v>
       </c>
-      <c r="I29" t="str">
+      <c r="I29" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C028</v>
       </c>
-      <c r="J29" t="str">
+      <c r="J29" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ananya</v>
       </c>
-      <c r="K29" t="str">
+      <c r="K29" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B29, " "), {"#",";","_","-"})</f>
         <v>Gupta</v>
       </c>
-      <c r="L29" t="str" cm="1">
+      <c r="L29" s="4" t="str" cm="1">
         <f t="array" ref="L29">LEFT(_xlfn.CONCAT(IFERROR(MID(B29, _xlfn.SEQUENCE(LEN(B29)), 1) + 0, "")), 10)</f>
         <v>1000000028</v>
       </c>
-      <c r="M29" t="str" cm="1">
+      <c r="M29" s="6" t="str" cm="1">
         <f t="array" ref="M29">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C29, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -3918,7 +3947,7 @@
 )</f>
         <v>ananyagupta1000000028@gmail.com</v>
       </c>
-      <c r="N29" t="str" cm="1">
+      <c r="N29" s="4" t="str" cm="1">
         <f t="array" ref="N29:O29">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D29, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -3928,10 +3957,10 @@
 )</f>
         <v>Mumbai</v>
       </c>
-      <c r="O29" t="str">
+      <c r="O29" s="4" t="str">
         <v>500028</v>
       </c>
-      <c r="P29" s="3" cm="1">
+      <c r="P29" s="5" cm="1">
         <f t="array" ref="P29">_xlfn.LET(
     _xlpm.val, TRIM(E29),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -3950,11 +3979,11 @@
 )</f>
         <v>45661</v>
       </c>
-      <c r="Q29" t="str" cm="1">
+      <c r="Q29" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q29" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F29, ROW(INDIRECT("1:" &amp; LEN(F29))), 1) * 1, ""))</f>
         <v>50028</v>
       </c>
-      <c r="R29" t="str" cm="1">
+      <c r="R29" s="4" t="str" cm="1">
         <f t="array" ref="R29">TRIM(_xlfn.REDUCE(G29, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>followuphigh</v>
       </c>
@@ -3981,23 +4010,23 @@
       <c r="G30" t="s">
         <v>40</v>
       </c>
-      <c r="I30" t="str">
+      <c r="I30" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C029</v>
       </c>
-      <c r="J30" t="str">
+      <c r="J30" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Rohan</v>
       </c>
-      <c r="K30" t="str">
+      <c r="K30" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B30, " "), {"#",";","_","-"})</f>
         <v>Iyer</v>
       </c>
-      <c r="L30" t="str" cm="1">
+      <c r="L30" s="4" t="str" cm="1">
         <f t="array" ref="L30">LEFT(_xlfn.CONCAT(IFERROR(MID(B30, _xlfn.SEQUENCE(LEN(B30)), 1) + 0, "")), 10)</f>
         <v>1000000029</v>
       </c>
-      <c r="M30" t="str" cm="1">
+      <c r="M30" s="6" t="str" cm="1">
         <f t="array" ref="M30">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C30, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -4008,7 +4037,7 @@
 )</f>
         <v>rohaniyer1000000029@gmail.com</v>
       </c>
-      <c r="N30" t="str" cm="1">
+      <c r="N30" s="4" t="str" cm="1">
         <f t="array" ref="N30:O30">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D30, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -4018,10 +4047,10 @@
 )</f>
         <v>Delhi</v>
       </c>
-      <c r="O30" t="str">
+      <c r="O30" s="4" t="str">
         <v>500029</v>
       </c>
-      <c r="P30" s="3" cm="1">
+      <c r="P30" s="5" cm="1">
         <f t="array" ref="P30">_xlfn.LET(
     _xlpm.val, TRIM(E30),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -4040,11 +4069,11 @@
 )</f>
         <v>45662</v>
       </c>
-      <c r="Q30" t="str" cm="1">
+      <c r="Q30" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q30" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F30, ROW(INDIRECT("1:" &amp; LEN(F30))), 1) * 1, ""))</f>
         <v>50029</v>
       </c>
-      <c r="R30" t="str" cm="1">
+      <c r="R30" s="4" t="str" cm="1">
         <f t="array" ref="R30">TRIM(_xlfn.REDUCE(G30, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>urgent</v>
       </c>
@@ -4071,23 +4100,23 @@
       <c r="G31" t="s">
         <v>90</v>
       </c>
-      <c r="I31" t="str">
+      <c r="I31" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C030</v>
       </c>
-      <c r="J31" t="str">
+      <c r="J31" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Sneha</v>
       </c>
-      <c r="K31" t="str">
+      <c r="K31" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B31, " "), {"#",";","_","-"})</f>
         <v>Nair</v>
       </c>
-      <c r="L31" t="str" cm="1">
+      <c r="L31" s="4" t="str" cm="1">
         <f t="array" ref="L31">LEFT(_xlfn.CONCAT(IFERROR(MID(B31, _xlfn.SEQUENCE(LEN(B31)), 1) + 0, "")), 10)</f>
         <v>1000000030</v>
       </c>
-      <c r="M31" t="str" cm="1">
+      <c r="M31" s="6" t="str" cm="1">
         <f t="array" ref="M31">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C31, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -4098,7 +4127,7 @@
 )</f>
         <v>snehanair1000000030@gmail.com</v>
       </c>
-      <c r="N31" t="str" cm="1">
+      <c r="N31" s="4" t="str" cm="1">
         <f t="array" ref="N31:O31">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D31, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -4108,10 +4137,10 @@
 )</f>
         <v>Pune</v>
       </c>
-      <c r="O31" t="str">
+      <c r="O31" s="4" t="str">
         <v>500030</v>
       </c>
-      <c r="P31" s="3" cm="1">
+      <c r="P31" s="5" cm="1">
         <f t="array" ref="P31">_xlfn.LET(
     _xlpm.val, TRIM(E31),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -4130,11 +4159,11 @@
 )</f>
         <v>45663</v>
       </c>
-      <c r="Q31" t="str" cm="1">
+      <c r="Q31" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q31" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F31, ROW(INDIRECT("1:" &amp; LEN(F31))), 1) * 1, ""))</f>
         <v>50030</v>
       </c>
-      <c r="R31" t="str" cm="1">
+      <c r="R31" s="4" t="str" cm="1">
         <f t="array" ref="R31">TRIM(_xlfn.REDUCE(G31, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>new lead</v>
       </c>
@@ -4161,23 +4190,23 @@
       <c r="G32" t="s">
         <v>13</v>
       </c>
-      <c r="I32" t="str">
+      <c r="I32" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C031</v>
       </c>
-      <c r="J32" t="str">
+      <c r="J32" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Aarav</v>
       </c>
-      <c r="K32" t="str">
+      <c r="K32" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B32, " "), {"#",";","_","-"})</f>
         <v>Mehta</v>
       </c>
-      <c r="L32" t="str" cm="1">
+      <c r="L32" s="4" t="str" cm="1">
         <f t="array" ref="L32">LEFT(_xlfn.CONCAT(IFERROR(MID(B32, _xlfn.SEQUENCE(LEN(B32)), 1) + 0, "")), 10)</f>
         <v>1000000031</v>
       </c>
-      <c r="M32" t="str" cm="1">
+      <c r="M32" s="6" t="str" cm="1">
         <f t="array" ref="M32">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C32, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -4188,7 +4217,7 @@
 )</f>
         <v>aaravmehta1000000031@gmail.com</v>
       </c>
-      <c r="N32" t="str" cm="1">
+      <c r="N32" s="4" t="str" cm="1">
         <f t="array" ref="N32:O32">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D32, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -4198,10 +4227,10 @@
 )</f>
         <v>Chennai</v>
       </c>
-      <c r="O32" t="str">
+      <c r="O32" s="4" t="str">
         <v>500031</v>
       </c>
-      <c r="P32" s="3" cm="1">
+      <c r="P32" s="5" cm="1">
         <f t="array" ref="P32">_xlfn.LET(
     _xlpm.val, TRIM(E32),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -4220,11 +4249,11 @@
 )</f>
         <v>45664</v>
       </c>
-      <c r="Q32" t="str" cm="1">
+      <c r="Q32" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q32" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F32, ROW(INDIRECT("1:" &amp; LEN(F32))), 1) * 1, ""))</f>
         <v>50031</v>
       </c>
-      <c r="R32" t="str" cm="1">
+      <c r="R32" s="4" t="str" cm="1">
         <f t="array" ref="R32">TRIM(_xlfn.REDUCE(G32, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>call later</v>
       </c>
@@ -4251,23 +4280,23 @@
       <c r="G33" t="s">
         <v>33</v>
       </c>
-      <c r="I33" t="str">
+      <c r="I33" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C032</v>
       </c>
-      <c r="J33" t="str">
+      <c r="J33" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Diya</v>
       </c>
-      <c r="K33" t="str">
+      <c r="K33" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B33, " "), {"#",";","_","-"})</f>
         <v>Sharma</v>
       </c>
-      <c r="L33" t="str" cm="1">
+      <c r="L33" s="4" t="str" cm="1">
         <f t="array" ref="L33">LEFT(_xlfn.CONCAT(IFERROR(MID(B33, _xlfn.SEQUENCE(LEN(B33)), 1) + 0, "")), 10)</f>
         <v>1000000032</v>
       </c>
-      <c r="M33" t="str" cm="1">
+      <c r="M33" s="6" t="str" cm="1">
         <f t="array" ref="M33">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C33, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -4278,7 +4307,7 @@
 )</f>
         <v>diyasharma1000000032@gmail.com</v>
       </c>
-      <c r="N33" t="str" cm="1">
+      <c r="N33" s="4" t="str" cm="1">
         <f t="array" ref="N33:O33">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D33, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -4288,10 +4317,10 @@
 )</f>
         <v>Bangalore</v>
       </c>
-      <c r="O33" t="str">
+      <c r="O33" s="4" t="str">
         <v>500032</v>
       </c>
-      <c r="P33" s="3" cm="1">
+      <c r="P33" s="5" cm="1">
         <f t="array" ref="P33">_xlfn.LET(
     _xlpm.val, TRIM(E33),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -4310,11 +4339,11 @@
 )</f>
         <v>45665</v>
       </c>
-      <c r="Q33" t="str" cm="1">
+      <c r="Q33" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q33" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F33, ROW(INDIRECT("1:" &amp; LEN(F33))), 1) * 1, ""))</f>
         <v>50032</v>
       </c>
-      <c r="R33" t="str" cm="1">
+      <c r="R33" s="4" t="str" cm="1">
         <f t="array" ref="R33">TRIM(_xlfn.REDUCE(G33, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>VIP client</v>
       </c>
@@ -4341,23 +4370,23 @@
       <c r="G34" t="s">
         <v>47</v>
       </c>
-      <c r="I34" t="str">
+      <c r="I34" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C033</v>
       </c>
-      <c r="J34" t="str">
+      <c r="J34" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kabir</v>
       </c>
-      <c r="K34" t="str">
+      <c r="K34" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B34, " "), {"#",";","_","-"})</f>
         <v>Verma</v>
       </c>
-      <c r="L34" t="str" cm="1">
+      <c r="L34" s="4" t="str" cm="1">
         <f t="array" ref="L34">LEFT(_xlfn.CONCAT(IFERROR(MID(B34, _xlfn.SEQUENCE(LEN(B34)), 1) + 0, "")), 10)</f>
         <v>1000000033</v>
       </c>
-      <c r="M34" t="str" cm="1">
+      <c r="M34" s="6" t="str" cm="1">
         <f t="array" ref="M34">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C34, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -4368,7 +4397,7 @@
 )</f>
         <v>kabirverma1000000033@gmail.com</v>
       </c>
-      <c r="N34" t="str" cm="1">
+      <c r="N34" s="4" t="str" cm="1">
         <f t="array" ref="N34:O34">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D34, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -4378,10 +4407,10 @@
 )</f>
         <v>Hyderabad</v>
       </c>
-      <c r="O34" t="str">
+      <c r="O34" s="4" t="str">
         <v>500033</v>
       </c>
-      <c r="P34" s="3" cm="1">
+      <c r="P34" s="5" cm="1">
         <f t="array" ref="P34">_xlfn.LET(
     _xlpm.val, TRIM(E34),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -4400,11 +4429,11 @@
 )</f>
         <v>45666</v>
       </c>
-      <c r="Q34" t="str" cm="1">
+      <c r="Q34" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q34" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F34, ROW(INDIRECT("1:" &amp; LEN(F34))), 1) * 1, ""))</f>
         <v>50033</v>
       </c>
-      <c r="R34" t="str" cm="1">
+      <c r="R34" s="4" t="str" cm="1">
         <f t="array" ref="R34">TRIM(_xlfn.REDUCE(G34, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>pending</v>
       </c>
@@ -4431,23 +4460,23 @@
       <c r="G35" t="s">
         <v>26</v>
       </c>
-      <c r="I35" t="str">
+      <c r="I35" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C034</v>
       </c>
-      <c r="J35" t="str">
+      <c r="J35" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ananya</v>
       </c>
-      <c r="K35" t="str">
+      <c r="K35" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B35, " "), {"#",";","_","-"})</f>
         <v>Gupta</v>
       </c>
-      <c r="L35" t="str" cm="1">
+      <c r="L35" s="4" t="str" cm="1">
         <f t="array" ref="L35">LEFT(_xlfn.CONCAT(IFERROR(MID(B35, _xlfn.SEQUENCE(LEN(B35)), 1) + 0, "")), 10)</f>
         <v>1000000034</v>
       </c>
-      <c r="M35" t="str" cm="1">
+      <c r="M35" s="6" t="str" cm="1">
         <f t="array" ref="M35">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C35, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -4458,7 +4487,7 @@
 )</f>
         <v>ananyagupta1000000034@gmail.com</v>
       </c>
-      <c r="N35" t="str" cm="1">
+      <c r="N35" s="4" t="str" cm="1">
         <f t="array" ref="N35:O35">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D35, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -4468,10 +4497,10 @@
 )</f>
         <v>Mumbai</v>
       </c>
-      <c r="O35" t="str">
+      <c r="O35" s="4" t="str">
         <v>500034</v>
       </c>
-      <c r="P35" s="3" cm="1">
+      <c r="P35" s="5" cm="1">
         <f t="array" ref="P35">_xlfn.LET(
     _xlpm.val, TRIM(E35),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -4490,11 +4519,11 @@
 )</f>
         <v>45667</v>
       </c>
-      <c r="Q35" t="str" cm="1">
+      <c r="Q35" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q35" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F35, ROW(INDIRECT("1:" &amp; LEN(F35))), 1) * 1, ""))</f>
         <v>50034</v>
       </c>
-      <c r="R35" t="str" cm="1">
+      <c r="R35" s="4" t="str" cm="1">
         <f t="array" ref="R35">TRIM(_xlfn.REDUCE(G35, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>followuphigh</v>
       </c>
@@ -4521,23 +4550,23 @@
       <c r="G36" t="s">
         <v>40</v>
       </c>
-      <c r="I36" t="str">
+      <c r="I36" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C035</v>
       </c>
-      <c r="J36" t="str">
+      <c r="J36" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Rohan</v>
       </c>
-      <c r="K36" t="str">
+      <c r="K36" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B36, " "), {"#",";","_","-"})</f>
         <v>Iyer</v>
       </c>
-      <c r="L36" t="str" cm="1">
+      <c r="L36" s="4" t="str" cm="1">
         <f t="array" ref="L36">LEFT(_xlfn.CONCAT(IFERROR(MID(B36, _xlfn.SEQUENCE(LEN(B36)), 1) + 0, "")), 10)</f>
         <v>1000000035</v>
       </c>
-      <c r="M36" t="str" cm="1">
+      <c r="M36" s="6" t="str" cm="1">
         <f t="array" ref="M36">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C36, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -4548,7 +4577,7 @@
 )</f>
         <v>rohaniyer1000000035@gmail.com</v>
       </c>
-      <c r="N36" t="str" cm="1">
+      <c r="N36" s="4" t="str" cm="1">
         <f t="array" ref="N36:O36">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D36, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -4558,10 +4587,10 @@
 )</f>
         <v>Delhi</v>
       </c>
-      <c r="O36" t="str">
+      <c r="O36" s="4" t="str">
         <v>500035</v>
       </c>
-      <c r="P36" s="3" cm="1">
+      <c r="P36" s="5" cm="1">
         <f t="array" ref="P36">_xlfn.LET(
     _xlpm.val, TRIM(E36),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -4580,11 +4609,11 @@
 )</f>
         <v>45668</v>
       </c>
-      <c r="Q36" t="str" cm="1">
+      <c r="Q36" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q36" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F36, ROW(INDIRECT("1:" &amp; LEN(F36))), 1) * 1, ""))</f>
         <v>50035</v>
       </c>
-      <c r="R36" t="str" cm="1">
+      <c r="R36" s="4" t="str" cm="1">
         <f t="array" ref="R36">TRIM(_xlfn.REDUCE(G36, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>urgent</v>
       </c>
@@ -4611,23 +4640,23 @@
       <c r="G37" t="s">
         <v>90</v>
       </c>
-      <c r="I37" t="str">
+      <c r="I37" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C036</v>
       </c>
-      <c r="J37" t="str">
+      <c r="J37" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Sneha</v>
       </c>
-      <c r="K37" t="str">
+      <c r="K37" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B37, " "), {"#",";","_","-"})</f>
         <v>Nair</v>
       </c>
-      <c r="L37" t="str" cm="1">
+      <c r="L37" s="4" t="str" cm="1">
         <f t="array" ref="L37">LEFT(_xlfn.CONCAT(IFERROR(MID(B37, _xlfn.SEQUENCE(LEN(B37)), 1) + 0, "")), 10)</f>
         <v>1000000036</v>
       </c>
-      <c r="M37" t="str" cm="1">
+      <c r="M37" s="6" t="str" cm="1">
         <f t="array" ref="M37">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C37, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -4638,7 +4667,7 @@
 )</f>
         <v>snehanair1000000036@gmail.com</v>
       </c>
-      <c r="N37" t="str" cm="1">
+      <c r="N37" s="4" t="str" cm="1">
         <f t="array" ref="N37:O37">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D37, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -4648,10 +4677,10 @@
 )</f>
         <v>Pune</v>
       </c>
-      <c r="O37" t="str">
+      <c r="O37" s="4" t="str">
         <v>500036</v>
       </c>
-      <c r="P37" s="3" cm="1">
+      <c r="P37" s="5" cm="1">
         <f t="array" ref="P37">_xlfn.LET(
     _xlpm.val, TRIM(E37),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -4670,11 +4699,11 @@
 )</f>
         <v>45669</v>
       </c>
-      <c r="Q37" t="str" cm="1">
+      <c r="Q37" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q37" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F37, ROW(INDIRECT("1:" &amp; LEN(F37))), 1) * 1, ""))</f>
         <v>50036</v>
       </c>
-      <c r="R37" t="str" cm="1">
+      <c r="R37" s="4" t="str" cm="1">
         <f t="array" ref="R37">TRIM(_xlfn.REDUCE(G37, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>new lead</v>
       </c>
@@ -4701,23 +4730,23 @@
       <c r="G38" t="s">
         <v>13</v>
       </c>
-      <c r="I38" t="str">
+      <c r="I38" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C037</v>
       </c>
-      <c r="J38" t="str">
+      <c r="J38" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Aarav</v>
       </c>
-      <c r="K38" t="str">
+      <c r="K38" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B38, " "), {"#",";","_","-"})</f>
         <v>Mehta</v>
       </c>
-      <c r="L38" t="str" cm="1">
+      <c r="L38" s="4" t="str" cm="1">
         <f t="array" ref="L38">LEFT(_xlfn.CONCAT(IFERROR(MID(B38, _xlfn.SEQUENCE(LEN(B38)), 1) + 0, "")), 10)</f>
         <v>1000000037</v>
       </c>
-      <c r="M38" t="str" cm="1">
+      <c r="M38" s="6" t="str" cm="1">
         <f t="array" ref="M38">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C38, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -4728,7 +4757,7 @@
 )</f>
         <v>aaravmehta1000000037@gmail.com</v>
       </c>
-      <c r="N38" t="str" cm="1">
+      <c r="N38" s="4" t="str" cm="1">
         <f t="array" ref="N38:O38">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D38, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -4738,10 +4767,10 @@
 )</f>
         <v>Chennai</v>
       </c>
-      <c r="O38" t="str">
+      <c r="O38" s="4" t="str">
         <v>500037</v>
       </c>
-      <c r="P38" s="3" cm="1">
+      <c r="P38" s="5" cm="1">
         <f t="array" ref="P38">_xlfn.LET(
     _xlpm.val, TRIM(E38),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -4760,11 +4789,11 @@
 )</f>
         <v>45670</v>
       </c>
-      <c r="Q38" t="str" cm="1">
+      <c r="Q38" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q38" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F38, ROW(INDIRECT("1:" &amp; LEN(F38))), 1) * 1, ""))</f>
         <v>50037</v>
       </c>
-      <c r="R38" t="str" cm="1">
+      <c r="R38" s="4" t="str" cm="1">
         <f t="array" ref="R38">TRIM(_xlfn.REDUCE(G38, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>call later</v>
       </c>
@@ -4791,23 +4820,23 @@
       <c r="G39" t="s">
         <v>33</v>
       </c>
-      <c r="I39" t="str">
+      <c r="I39" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C038</v>
       </c>
-      <c r="J39" t="str">
+      <c r="J39" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Diya</v>
       </c>
-      <c r="K39" t="str">
+      <c r="K39" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B39, " "), {"#",";","_","-"})</f>
         <v>Sharma</v>
       </c>
-      <c r="L39" t="str" cm="1">
+      <c r="L39" s="4" t="str" cm="1">
         <f t="array" ref="L39">LEFT(_xlfn.CONCAT(IFERROR(MID(B39, _xlfn.SEQUENCE(LEN(B39)), 1) + 0, "")), 10)</f>
         <v>1000000038</v>
       </c>
-      <c r="M39" t="str" cm="1">
+      <c r="M39" s="6" t="str" cm="1">
         <f t="array" ref="M39">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C39, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -4818,7 +4847,7 @@
 )</f>
         <v>diyasharma1000000038@gmail.com</v>
       </c>
-      <c r="N39" t="str" cm="1">
+      <c r="N39" s="4" t="str" cm="1">
         <f t="array" ref="N39:O39">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D39, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -4828,10 +4857,10 @@
 )</f>
         <v>Bangalore</v>
       </c>
-      <c r="O39" t="str">
+      <c r="O39" s="4" t="str">
         <v>500038</v>
       </c>
-      <c r="P39" s="3" cm="1">
+      <c r="P39" s="5" cm="1">
         <f t="array" ref="P39">_xlfn.LET(
     _xlpm.val, TRIM(E39),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -4850,11 +4879,11 @@
 )</f>
         <v>45671</v>
       </c>
-      <c r="Q39" t="str" cm="1">
+      <c r="Q39" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q39" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F39, ROW(INDIRECT("1:" &amp; LEN(F39))), 1) * 1, ""))</f>
         <v>50038</v>
       </c>
-      <c r="R39" t="str" cm="1">
+      <c r="R39" s="4" t="str" cm="1">
         <f t="array" ref="R39">TRIM(_xlfn.REDUCE(G39, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>VIP client</v>
       </c>
@@ -4881,23 +4910,23 @@
       <c r="G40" t="s">
         <v>47</v>
       </c>
-      <c r="I40" t="str">
+      <c r="I40" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C039</v>
       </c>
-      <c r="J40" t="str">
+      <c r="J40" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kabir</v>
       </c>
-      <c r="K40" t="str">
+      <c r="K40" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B40, " "), {"#",";","_","-"})</f>
         <v>Verma</v>
       </c>
-      <c r="L40" t="str" cm="1">
+      <c r="L40" s="4" t="str" cm="1">
         <f t="array" ref="L40">LEFT(_xlfn.CONCAT(IFERROR(MID(B40, _xlfn.SEQUENCE(LEN(B40)), 1) + 0, "")), 10)</f>
         <v>1000000039</v>
       </c>
-      <c r="M40" t="str" cm="1">
+      <c r="M40" s="6" t="str" cm="1">
         <f t="array" ref="M40">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C40, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -4908,7 +4937,7 @@
 )</f>
         <v>kabirverma1000000039@gmail.com</v>
       </c>
-      <c r="N40" t="str" cm="1">
+      <c r="N40" s="4" t="str" cm="1">
         <f t="array" ref="N40:O40">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D40, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -4918,10 +4947,10 @@
 )</f>
         <v>Hyderabad</v>
       </c>
-      <c r="O40" t="str">
+      <c r="O40" s="4" t="str">
         <v>500039</v>
       </c>
-      <c r="P40" s="3" cm="1">
+      <c r="P40" s="5" cm="1">
         <f t="array" ref="P40">_xlfn.LET(
     _xlpm.val, TRIM(E40),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -4940,11 +4969,11 @@
 )</f>
         <v>45672</v>
       </c>
-      <c r="Q40" t="str" cm="1">
+      <c r="Q40" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q40" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F40, ROW(INDIRECT("1:" &amp; LEN(F40))), 1) * 1, ""))</f>
         <v>50039</v>
       </c>
-      <c r="R40" t="str" cm="1">
+      <c r="R40" s="4" t="str" cm="1">
         <f t="array" ref="R40">TRIM(_xlfn.REDUCE(G40, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>pending</v>
       </c>
@@ -4971,23 +5000,23 @@
       <c r="G41" t="s">
         <v>26</v>
       </c>
-      <c r="I41" t="str">
+      <c r="I41" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C040</v>
       </c>
-      <c r="J41" t="str">
+      <c r="J41" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ananya</v>
       </c>
-      <c r="K41" t="str">
+      <c r="K41" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B41, " "), {"#",";","_","-"})</f>
         <v>Gupta</v>
       </c>
-      <c r="L41" t="str" cm="1">
+      <c r="L41" s="4" t="str" cm="1">
         <f t="array" ref="L41">LEFT(_xlfn.CONCAT(IFERROR(MID(B41, _xlfn.SEQUENCE(LEN(B41)), 1) + 0, "")), 10)</f>
         <v>1000000040</v>
       </c>
-      <c r="M41" t="str" cm="1">
+      <c r="M41" s="6" t="str" cm="1">
         <f t="array" ref="M41">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C41, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -4998,7 +5027,7 @@
 )</f>
         <v>ananyagupta1000000040@gmail.com</v>
       </c>
-      <c r="N41" t="str" cm="1">
+      <c r="N41" s="4" t="str" cm="1">
         <f t="array" ref="N41:O41">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D41, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -5008,10 +5037,10 @@
 )</f>
         <v>Mumbai</v>
       </c>
-      <c r="O41" t="str">
+      <c r="O41" s="4" t="str">
         <v>500040</v>
       </c>
-      <c r="P41" s="3" cm="1">
+      <c r="P41" s="5" cm="1">
         <f t="array" ref="P41">_xlfn.LET(
     _xlpm.val, TRIM(E41),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -5030,11 +5059,11 @@
 )</f>
         <v>45673</v>
       </c>
-      <c r="Q41" t="str" cm="1">
+      <c r="Q41" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q41" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F41, ROW(INDIRECT("1:" &amp; LEN(F41))), 1) * 1, ""))</f>
         <v>50040</v>
       </c>
-      <c r="R41" t="str" cm="1">
+      <c r="R41" s="4" t="str" cm="1">
         <f t="array" ref="R41">TRIM(_xlfn.REDUCE(G41, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>followuphigh</v>
       </c>
@@ -5061,23 +5090,23 @@
       <c r="G42" t="s">
         <v>40</v>
       </c>
-      <c r="I42" t="str">
+      <c r="I42" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C041</v>
       </c>
-      <c r="J42" t="str">
+      <c r="J42" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Rohan</v>
       </c>
-      <c r="K42" t="str">
+      <c r="K42" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B42, " "), {"#",";","_","-"})</f>
         <v>Iyer</v>
       </c>
-      <c r="L42" t="str" cm="1">
+      <c r="L42" s="4" t="str" cm="1">
         <f t="array" ref="L42">LEFT(_xlfn.CONCAT(IFERROR(MID(B42, _xlfn.SEQUENCE(LEN(B42)), 1) + 0, "")), 10)</f>
         <v>1000000041</v>
       </c>
-      <c r="M42" t="str" cm="1">
+      <c r="M42" s="6" t="str" cm="1">
         <f t="array" ref="M42">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C42, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -5088,7 +5117,7 @@
 )</f>
         <v>rohaniyer1000000041@gmail.com</v>
       </c>
-      <c r="N42" t="str" cm="1">
+      <c r="N42" s="4" t="str" cm="1">
         <f t="array" ref="N42:O42">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D42, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -5098,10 +5127,10 @@
 )</f>
         <v>Delhi</v>
       </c>
-      <c r="O42" t="str">
+      <c r="O42" s="4" t="str">
         <v>500041</v>
       </c>
-      <c r="P42" s="3" cm="1">
+      <c r="P42" s="5" cm="1">
         <f t="array" ref="P42">_xlfn.LET(
     _xlpm.val, TRIM(E42),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -5120,11 +5149,11 @@
 )</f>
         <v>45674</v>
       </c>
-      <c r="Q42" t="str" cm="1">
+      <c r="Q42" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q42" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F42, ROW(INDIRECT("1:" &amp; LEN(F42))), 1) * 1, ""))</f>
         <v>50041</v>
       </c>
-      <c r="R42" t="str" cm="1">
+      <c r="R42" s="4" t="str" cm="1">
         <f t="array" ref="R42">TRIM(_xlfn.REDUCE(G42, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>urgent</v>
       </c>
@@ -5151,23 +5180,23 @@
       <c r="G43" t="s">
         <v>90</v>
       </c>
-      <c r="I43" t="str">
+      <c r="I43" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C042</v>
       </c>
-      <c r="J43" t="str">
+      <c r="J43" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Sneha</v>
       </c>
-      <c r="K43" t="str">
+      <c r="K43" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B43, " "), {"#",";","_","-"})</f>
         <v>Nair</v>
       </c>
-      <c r="L43" t="str" cm="1">
+      <c r="L43" s="4" t="str" cm="1">
         <f t="array" ref="L43">LEFT(_xlfn.CONCAT(IFERROR(MID(B43, _xlfn.SEQUENCE(LEN(B43)), 1) + 0, "")), 10)</f>
         <v>1000000042</v>
       </c>
-      <c r="M43" t="str" cm="1">
+      <c r="M43" s="6" t="str" cm="1">
         <f t="array" ref="M43">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C43, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -5178,7 +5207,7 @@
 )</f>
         <v>snehanair1000000042@gmail.com</v>
       </c>
-      <c r="N43" t="str" cm="1">
+      <c r="N43" s="4" t="str" cm="1">
         <f t="array" ref="N43:O43">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D43, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -5188,10 +5217,10 @@
 )</f>
         <v>Pune</v>
       </c>
-      <c r="O43" t="str">
+      <c r="O43" s="4" t="str">
         <v>500042</v>
       </c>
-      <c r="P43" s="3" cm="1">
+      <c r="P43" s="5" cm="1">
         <f t="array" ref="P43">_xlfn.LET(
     _xlpm.val, TRIM(E43),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -5210,11 +5239,11 @@
 )</f>
         <v>45675</v>
       </c>
-      <c r="Q43" t="str" cm="1">
+      <c r="Q43" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q43" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F43, ROW(INDIRECT("1:" &amp; LEN(F43))), 1) * 1, ""))</f>
         <v>50042</v>
       </c>
-      <c r="R43" t="str" cm="1">
+      <c r="R43" s="4" t="str" cm="1">
         <f t="array" ref="R43">TRIM(_xlfn.REDUCE(G43, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>new lead</v>
       </c>
@@ -5241,23 +5270,23 @@
       <c r="G44" t="s">
         <v>13</v>
       </c>
-      <c r="I44" t="str">
+      <c r="I44" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C043</v>
       </c>
-      <c r="J44" t="str">
+      <c r="J44" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Aarav</v>
       </c>
-      <c r="K44" t="str">
+      <c r="K44" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B44, " "), {"#",";","_","-"})</f>
         <v>Mehta</v>
       </c>
-      <c r="L44" t="str" cm="1">
+      <c r="L44" s="4" t="str" cm="1">
         <f t="array" ref="L44">LEFT(_xlfn.CONCAT(IFERROR(MID(B44, _xlfn.SEQUENCE(LEN(B44)), 1) + 0, "")), 10)</f>
         <v>1000000043</v>
       </c>
-      <c r="M44" t="str" cm="1">
+      <c r="M44" s="6" t="str" cm="1">
         <f t="array" ref="M44">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C44, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -5268,7 +5297,7 @@
 )</f>
         <v>aaravmehta1000000043@gmail.com</v>
       </c>
-      <c r="N44" t="str" cm="1">
+      <c r="N44" s="4" t="str" cm="1">
         <f t="array" ref="N44:O44">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D44, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -5278,10 +5307,10 @@
 )</f>
         <v>Chennai</v>
       </c>
-      <c r="O44" t="str">
+      <c r="O44" s="4" t="str">
         <v>500043</v>
       </c>
-      <c r="P44" s="3" cm="1">
+      <c r="P44" s="5" cm="1">
         <f t="array" ref="P44">_xlfn.LET(
     _xlpm.val, TRIM(E44),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -5300,11 +5329,11 @@
 )</f>
         <v>45676</v>
       </c>
-      <c r="Q44" t="str" cm="1">
+      <c r="Q44" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q44" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F44, ROW(INDIRECT("1:" &amp; LEN(F44))), 1) * 1, ""))</f>
         <v>50043</v>
       </c>
-      <c r="R44" t="str" cm="1">
+      <c r="R44" s="4" t="str" cm="1">
         <f t="array" ref="R44">TRIM(_xlfn.REDUCE(G44, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>call later</v>
       </c>
@@ -5331,23 +5360,23 @@
       <c r="G45" t="s">
         <v>33</v>
       </c>
-      <c r="I45" t="str">
+      <c r="I45" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C044</v>
       </c>
-      <c r="J45" t="str">
+      <c r="J45" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Diya</v>
       </c>
-      <c r="K45" t="str">
+      <c r="K45" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B45, " "), {"#",";","_","-"})</f>
         <v>Sharma</v>
       </c>
-      <c r="L45" t="str" cm="1">
+      <c r="L45" s="4" t="str" cm="1">
         <f t="array" ref="L45">LEFT(_xlfn.CONCAT(IFERROR(MID(B45, _xlfn.SEQUENCE(LEN(B45)), 1) + 0, "")), 10)</f>
         <v>1000000044</v>
       </c>
-      <c r="M45" t="str" cm="1">
+      <c r="M45" s="6" t="str" cm="1">
         <f t="array" ref="M45">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C45, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -5358,7 +5387,7 @@
 )</f>
         <v>diyasharma1000000044@gmail.com</v>
       </c>
-      <c r="N45" t="str" cm="1">
+      <c r="N45" s="4" t="str" cm="1">
         <f t="array" ref="N45:O45">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D45, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -5368,10 +5397,10 @@
 )</f>
         <v>Bangalore</v>
       </c>
-      <c r="O45" t="str">
+      <c r="O45" s="4" t="str">
         <v>500044</v>
       </c>
-      <c r="P45" s="3" cm="1">
+      <c r="P45" s="5" cm="1">
         <f t="array" ref="P45">_xlfn.LET(
     _xlpm.val, TRIM(E45),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -5390,11 +5419,11 @@
 )</f>
         <v>45677</v>
       </c>
-      <c r="Q45" t="str" cm="1">
+      <c r="Q45" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q45" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F45, ROW(INDIRECT("1:" &amp; LEN(F45))), 1) * 1, ""))</f>
         <v>50044</v>
       </c>
-      <c r="R45" t="str" cm="1">
+      <c r="R45" s="4" t="str" cm="1">
         <f t="array" ref="R45">TRIM(_xlfn.REDUCE(G45, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>VIP client</v>
       </c>
@@ -5421,23 +5450,23 @@
       <c r="G46" t="s">
         <v>47</v>
       </c>
-      <c r="I46" t="str">
+      <c r="I46" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C045</v>
       </c>
-      <c r="J46" t="str">
+      <c r="J46" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kabir</v>
       </c>
-      <c r="K46" t="str">
+      <c r="K46" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B46, " "), {"#",";","_","-"})</f>
         <v>Verma</v>
       </c>
-      <c r="L46" t="str" cm="1">
+      <c r="L46" s="4" t="str" cm="1">
         <f t="array" ref="L46">LEFT(_xlfn.CONCAT(IFERROR(MID(B46, _xlfn.SEQUENCE(LEN(B46)), 1) + 0, "")), 10)</f>
         <v>1000000045</v>
       </c>
-      <c r="M46" t="str" cm="1">
+      <c r="M46" s="6" t="str" cm="1">
         <f t="array" ref="M46">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C46, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -5448,7 +5477,7 @@
 )</f>
         <v>kabirverma1000000045@gmail.com</v>
       </c>
-      <c r="N46" t="str" cm="1">
+      <c r="N46" s="4" t="str" cm="1">
         <f t="array" ref="N46:O46">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D46, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -5458,10 +5487,10 @@
 )</f>
         <v>Hyderabad</v>
       </c>
-      <c r="O46" t="str">
+      <c r="O46" s="4" t="str">
         <v>500045</v>
       </c>
-      <c r="P46" s="3" cm="1">
+      <c r="P46" s="5" cm="1">
         <f t="array" ref="P46">_xlfn.LET(
     _xlpm.val, TRIM(E46),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -5480,11 +5509,11 @@
 )</f>
         <v>45678</v>
       </c>
-      <c r="Q46" t="str" cm="1">
+      <c r="Q46" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q46" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F46, ROW(INDIRECT("1:" &amp; LEN(F46))), 1) * 1, ""))</f>
         <v>50045</v>
       </c>
-      <c r="R46" t="str" cm="1">
+      <c r="R46" s="4" t="str" cm="1">
         <f t="array" ref="R46">TRIM(_xlfn.REDUCE(G46, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>pending</v>
       </c>
@@ -5511,23 +5540,23 @@
       <c r="G47" t="s">
         <v>26</v>
       </c>
-      <c r="I47" t="str">
+      <c r="I47" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C046</v>
       </c>
-      <c r="J47" t="str">
+      <c r="J47" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ananya</v>
       </c>
-      <c r="K47" t="str">
+      <c r="K47" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B47, " "), {"#",";","_","-"})</f>
         <v>Gupta</v>
       </c>
-      <c r="L47" t="str" cm="1">
+      <c r="L47" s="4" t="str" cm="1">
         <f t="array" ref="L47">LEFT(_xlfn.CONCAT(IFERROR(MID(B47, _xlfn.SEQUENCE(LEN(B47)), 1) + 0, "")), 10)</f>
         <v>1000000046</v>
       </c>
-      <c r="M47" t="str" cm="1">
+      <c r="M47" s="6" t="str" cm="1">
         <f t="array" ref="M47">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C47, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -5538,7 +5567,7 @@
 )</f>
         <v>ananyagupta1000000046@gmail.com</v>
       </c>
-      <c r="N47" t="str" cm="1">
+      <c r="N47" s="4" t="str" cm="1">
         <f t="array" ref="N47:O47">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D47, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -5548,10 +5577,10 @@
 )</f>
         <v>Mumbai</v>
       </c>
-      <c r="O47" t="str">
+      <c r="O47" s="4" t="str">
         <v>500046</v>
       </c>
-      <c r="P47" s="3" cm="1">
+      <c r="P47" s="5" cm="1">
         <f t="array" ref="P47">_xlfn.LET(
     _xlpm.val, TRIM(E47),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -5570,11 +5599,11 @@
 )</f>
         <v>45679</v>
       </c>
-      <c r="Q47" t="str" cm="1">
+      <c r="Q47" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q47" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F47, ROW(INDIRECT("1:" &amp; LEN(F47))), 1) * 1, ""))</f>
         <v>50046</v>
       </c>
-      <c r="R47" t="str" cm="1">
+      <c r="R47" s="4" t="str" cm="1">
         <f t="array" ref="R47">TRIM(_xlfn.REDUCE(G47, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>followuphigh</v>
       </c>
@@ -5601,23 +5630,23 @@
       <c r="G48" t="s">
         <v>40</v>
       </c>
-      <c r="I48" t="str">
+      <c r="I48" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C047</v>
       </c>
-      <c r="J48" t="str">
+      <c r="J48" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Rohan</v>
       </c>
-      <c r="K48" t="str">
+      <c r="K48" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B48, " "), {"#",";","_","-"})</f>
         <v>Iyer</v>
       </c>
-      <c r="L48" t="str" cm="1">
+      <c r="L48" s="4" t="str" cm="1">
         <f t="array" ref="L48">LEFT(_xlfn.CONCAT(IFERROR(MID(B48, _xlfn.SEQUENCE(LEN(B48)), 1) + 0, "")), 10)</f>
         <v>1000000047</v>
       </c>
-      <c r="M48" t="str" cm="1">
+      <c r="M48" s="6" t="str" cm="1">
         <f t="array" ref="M48">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C48, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -5628,7 +5657,7 @@
 )</f>
         <v>rohaniyer1000000047@gmail.com</v>
       </c>
-      <c r="N48" t="str" cm="1">
+      <c r="N48" s="4" t="str" cm="1">
         <f t="array" ref="N48:O48">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D48, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -5638,10 +5667,10 @@
 )</f>
         <v>Delhi</v>
       </c>
-      <c r="O48" t="str">
+      <c r="O48" s="4" t="str">
         <v>500047</v>
       </c>
-      <c r="P48" s="3" cm="1">
+      <c r="P48" s="5" cm="1">
         <f t="array" ref="P48">_xlfn.LET(
     _xlpm.val, TRIM(E48),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -5660,11 +5689,11 @@
 )</f>
         <v>45680</v>
       </c>
-      <c r="Q48" t="str" cm="1">
+      <c r="Q48" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q48" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F48, ROW(INDIRECT("1:" &amp; LEN(F48))), 1) * 1, ""))</f>
         <v>50047</v>
       </c>
-      <c r="R48" t="str" cm="1">
+      <c r="R48" s="4" t="str" cm="1">
         <f t="array" ref="R48">TRIM(_xlfn.REDUCE(G48, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>urgent</v>
       </c>
@@ -5691,23 +5720,23 @@
       <c r="G49" t="s">
         <v>90</v>
       </c>
-      <c r="I49" t="str">
+      <c r="I49" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C048</v>
       </c>
-      <c r="J49" t="str">
+      <c r="J49" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Sneha</v>
       </c>
-      <c r="K49" t="str">
+      <c r="K49" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B49, " "), {"#",";","_","-"})</f>
         <v>Nair</v>
       </c>
-      <c r="L49" t="str" cm="1">
+      <c r="L49" s="4" t="str" cm="1">
         <f t="array" ref="L49">LEFT(_xlfn.CONCAT(IFERROR(MID(B49, _xlfn.SEQUENCE(LEN(B49)), 1) + 0, "")), 10)</f>
         <v>1000000048</v>
       </c>
-      <c r="M49" t="str" cm="1">
+      <c r="M49" s="6" t="str" cm="1">
         <f t="array" ref="M49">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C49, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -5718,7 +5747,7 @@
 )</f>
         <v>snehanair1000000048@gmail.com</v>
       </c>
-      <c r="N49" t="str" cm="1">
+      <c r="N49" s="4" t="str" cm="1">
         <f t="array" ref="N49:O49">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D49, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -5728,10 +5757,10 @@
 )</f>
         <v>Pune</v>
       </c>
-      <c r="O49" t="str">
+      <c r="O49" s="4" t="str">
         <v>500048</v>
       </c>
-      <c r="P49" s="3" cm="1">
+      <c r="P49" s="5" cm="1">
         <f t="array" ref="P49">_xlfn.LET(
     _xlpm.val, TRIM(E49),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -5750,11 +5779,11 @@
 )</f>
         <v>45681</v>
       </c>
-      <c r="Q49" t="str" cm="1">
+      <c r="Q49" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q49" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F49, ROW(INDIRECT("1:" &amp; LEN(F49))), 1) * 1, ""))</f>
         <v>50048</v>
       </c>
-      <c r="R49" t="str" cm="1">
+      <c r="R49" s="4" t="str" cm="1">
         <f t="array" ref="R49">TRIM(_xlfn.REDUCE(G49, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>new lead</v>
       </c>
@@ -5781,23 +5810,23 @@
       <c r="G50" t="s">
         <v>13</v>
       </c>
-      <c r="I50" t="str">
+      <c r="I50" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C049</v>
       </c>
-      <c r="J50" t="str">
+      <c r="J50" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Aarav</v>
       </c>
-      <c r="K50" t="str">
+      <c r="K50" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B50, " "), {"#",";","_","-"})</f>
         <v>Mehta</v>
       </c>
-      <c r="L50" t="str" cm="1">
+      <c r="L50" s="4" t="str" cm="1">
         <f t="array" ref="L50">LEFT(_xlfn.CONCAT(IFERROR(MID(B50, _xlfn.SEQUENCE(LEN(B50)), 1) + 0, "")), 10)</f>
         <v>1000000049</v>
       </c>
-      <c r="M50" t="str" cm="1">
+      <c r="M50" s="6" t="str" cm="1">
         <f t="array" ref="M50">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C50, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -5808,7 +5837,7 @@
 )</f>
         <v>aaravmehta1000000049@gmail.com</v>
       </c>
-      <c r="N50" t="str" cm="1">
+      <c r="N50" s="4" t="str" cm="1">
         <f t="array" ref="N50:O50">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D50, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -5818,10 +5847,10 @@
 )</f>
         <v>Chennai</v>
       </c>
-      <c r="O50" t="str">
+      <c r="O50" s="4" t="str">
         <v>500049</v>
       </c>
-      <c r="P50" s="3" cm="1">
+      <c r="P50" s="5" cm="1">
         <f t="array" ref="P50">_xlfn.LET(
     _xlpm.val, TRIM(E50),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -5840,11 +5869,11 @@
 )</f>
         <v>45682</v>
       </c>
-      <c r="Q50" t="str" cm="1">
+      <c r="Q50" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q50" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F50, ROW(INDIRECT("1:" &amp; LEN(F50))), 1) * 1, ""))</f>
         <v>50049</v>
       </c>
-      <c r="R50" t="str" cm="1">
+      <c r="R50" s="4" t="str" cm="1">
         <f t="array" ref="R50">TRIM(_xlfn.REDUCE(G50, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>call later</v>
       </c>
@@ -5871,23 +5900,23 @@
       <c r="G51" t="s">
         <v>33</v>
       </c>
-      <c r="I51" t="str">
+      <c r="I51" s="4" t="str">
         <f t="shared" si="0"/>
         <v>C050</v>
       </c>
-      <c r="J51" t="str">
+      <c r="J51" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Diya</v>
       </c>
-      <c r="K51" t="str">
+      <c r="K51" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(B51, " "), {"#",";","_","-"})</f>
         <v>Sharma</v>
       </c>
-      <c r="L51" t="str" cm="1">
+      <c r="L51" s="4" t="str" cm="1">
         <f t="array" ref="L51">LEFT(_xlfn.CONCAT(IFERROR(MID(B51, _xlfn.SEQUENCE(LEN(B51)), 1) + 0, "")), 10)</f>
         <v>1000000050</v>
       </c>
-      <c r="M51" t="str" cm="1">
+      <c r="M51" s="6" t="str" cm="1">
         <f t="array" ref="M51">_xlfn.LET(
     _xlpm.rawEmail, SUBSTITUTE(C51, " ", ""),
     _xlpm.uName, _xlfn.TEXTBEFORE(_xlpm.rawEmail, "@"),
@@ -5898,7 +5927,7 @@
 )</f>
         <v>diyasharma1000000050@gmail.com</v>
       </c>
-      <c r="N51" t="str" cm="1">
+      <c r="N51" s="4" t="str" cm="1">
         <f t="array" ref="N51:O51">_xlfn.LET(
     _xlpm.raw, SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D51, ";", " "), "#", " "), "_", " "), "-", " "),
     _xlpm.clean, TRIM(_xlpm.raw),
@@ -5908,10 +5937,10 @@
 )</f>
         <v>Bangalore</v>
       </c>
-      <c r="O51" t="str">
+      <c r="O51" s="4" t="str">
         <v>500050</v>
       </c>
-      <c r="P51" s="3" cm="1">
+      <c r="P51" s="5" cm="1">
         <f t="array" ref="P51">_xlfn.LET(
     _xlpm.val, TRIM(E51),
     _xlpm.isHyphen, ISNUMBER(SEARCH("-", _xlpm.val)),
@@ -5930,11 +5959,11 @@
 )</f>
         <v>45683</v>
       </c>
-      <c r="Q51" t="str" cm="1">
+      <c r="Q51" s="4" t="str" cm="1">
         <f t="array" aca="1" ref="Q51" ca="1">_xlfn.TEXTJOIN("", TRUE, IFERROR(MID(F51, ROW(INDIRECT("1:" &amp; LEN(F51))), 1) * 1, ""))</f>
         <v>50050</v>
       </c>
-      <c r="R51" t="str" cm="1">
+      <c r="R51" s="4" t="str" cm="1">
         <f t="array" ref="R51">TRIM(_xlfn.REDUCE(G51, {"@",", ","!"}, _xlfn.LAMBDA(_xlpm.a,_xlpm.b, SUBSTITUTE(_xlpm.a, _xlpm.b, ""))))</f>
         <v>VIP client</v>
       </c>
@@ -5959,43 +5988,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="str">
+      <c r="A1" s="3" t="str">
         <f>'OLD Data'!I1</f>
         <v>ID</v>
       </c>
-      <c r="B1" s="4" t="str">
+      <c r="B1" s="3" t="str">
         <f>'OLD Data'!J1</f>
         <v>First Name</v>
       </c>
-      <c r="C1" s="4" t="str">
+      <c r="C1" s="3" t="str">
         <f>'OLD Data'!K1</f>
         <v>Last Name</v>
       </c>
-      <c r="D1" s="4" t="str">
+      <c r="D1" s="3" t="str">
         <f>'OLD Data'!L1</f>
         <v>Phone No</v>
       </c>
-      <c r="E1" s="4" t="str">
+      <c r="E1" s="3" t="str">
         <f>'OLD Data'!M1</f>
         <v>Email ID</v>
       </c>
-      <c r="F1" s="4" t="str">
+      <c r="F1" s="3" t="str">
         <f>'OLD Data'!N1</f>
         <v>Location</v>
       </c>
-      <c r="G1" s="4" t="str">
+      <c r="G1" s="3" t="str">
         <f>'OLD Data'!O1</f>
         <v>Pincode</v>
       </c>
-      <c r="H1" s="4" t="str">
+      <c r="H1" s="3" t="str">
         <f>'OLD Data'!P1</f>
         <v>Date</v>
       </c>
-      <c r="I1" s="4" t="str">
+      <c r="I1" s="3" t="str">
         <f>'OLD Data'!Q1</f>
         <v>Sales</v>
       </c>
-      <c r="J1" s="4" t="str">
+      <c r="J1" s="3" t="str">
         <f>'OLD Data'!R1</f>
         <v>Notes</v>
       </c>
@@ -6029,7 +6058,7 @@
         <f>'OLD Data'!O2</f>
         <v>600674</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="2">
         <f>'OLD Data'!P2</f>
         <v>45669</v>
       </c>
@@ -6071,7 +6100,7 @@
         <f>'OLD Data'!O3</f>
         <v>600332</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="2">
         <f>'OLD Data'!P3</f>
         <v>45676</v>
       </c>
@@ -6113,7 +6142,7 @@
         <f>'OLD Data'!O4</f>
         <v>560559</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="2">
         <f>'OLD Data'!P4</f>
         <v>45664</v>
       </c>
@@ -6155,7 +6184,7 @@
         <f>'OLD Data'!O5</f>
         <v>560595</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <f>'OLD Data'!P5</f>
         <v>45664</v>
       </c>
@@ -6197,7 +6226,7 @@
         <f>'OLD Data'!O6</f>
         <v>560045</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="2">
         <f>'OLD Data'!P6</f>
         <v>45675</v>
       </c>
@@ -6239,7 +6268,7 @@
         <f>'OLD Data'!O7</f>
         <v>110928</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="2">
         <f>'OLD Data'!P7</f>
         <v>45661</v>
       </c>
@@ -6281,7 +6310,7 @@
         <f>'OLD Data'!O8</f>
         <v>500929</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="2">
         <f>'OLD Data'!P8</f>
         <v>45673</v>
       </c>
@@ -6323,7 +6352,7 @@
         <f>'OLD Data'!O9</f>
         <v>400209</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="2">
         <f>'OLD Data'!P9</f>
         <v>45684</v>
       </c>
@@ -6365,7 +6394,7 @@
         <f>'OLD Data'!O10</f>
         <v>500725</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="2">
         <f>'OLD Data'!P10</f>
         <v>45667</v>
       </c>
@@ -6407,7 +6436,7 @@
         <f>'OLD Data'!O11</f>
         <v>560940</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="2">
         <f>'OLD Data'!P11</f>
         <v>45662</v>
       </c>
@@ -6449,7 +6478,7 @@
         <f>'OLD Data'!O12</f>
         <v>600883</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="2">
         <f>'OLD Data'!P12</f>
         <v>45666</v>
       </c>
@@ -6491,7 +6520,7 @@
         <f>'OLD Data'!O13</f>
         <v>110689</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="2">
         <f>'OLD Data'!P13</f>
         <v>45685</v>
       </c>
@@ -6533,7 +6562,7 @@
         <f>'OLD Data'!O14</f>
         <v>411529</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="2">
         <f>'OLD Data'!P14</f>
         <v>45666</v>
       </c>
@@ -6575,7 +6604,7 @@
         <f>'OLD Data'!O15</f>
         <v>560059</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="2">
         <f>'OLD Data'!P15</f>
         <v>45685</v>
       </c>
@@ -6617,7 +6646,7 @@
         <f>'OLD Data'!O16</f>
         <v>400574</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="2">
         <f>'OLD Data'!P16</f>
         <v>45659</v>
       </c>
@@ -6659,7 +6688,7 @@
         <f>'OLD Data'!O17</f>
         <v>560201</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="2">
         <f>'OLD Data'!P17</f>
         <v>45670</v>
       </c>
@@ -6701,7 +6730,7 @@
         <f>'OLD Data'!O18</f>
         <v>600667</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="2">
         <f>'OLD Data'!P18</f>
         <v>45663</v>
       </c>
@@ -6743,7 +6772,7 @@
         <f>'OLD Data'!O19</f>
         <v>560156</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="2">
         <f>'OLD Data'!P19</f>
         <v>45668</v>
       </c>
@@ -6785,7 +6814,7 @@
         <f>'OLD Data'!O20</f>
         <v>560586</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="2">
         <f>'OLD Data'!P20</f>
         <v>45661</v>
       </c>
@@ -6827,7 +6856,7 @@
         <f>'OLD Data'!O21</f>
         <v>500706</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="2">
         <f>'OLD Data'!P21</f>
         <v>45682</v>
       </c>
@@ -6869,7 +6898,7 @@
         <f>'OLD Data'!O22</f>
         <v>411481</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H22" s="2">
         <f>'OLD Data'!P22</f>
         <v>45672</v>
       </c>
@@ -6911,7 +6940,7 @@
         <f>'OLD Data'!O23</f>
         <v>500047</v>
       </c>
-      <c r="H23" s="3">
+      <c r="H23" s="2">
         <f>'OLD Data'!P23</f>
         <v>45669</v>
       </c>
@@ -6953,7 +6982,7 @@
         <f>'OLD Data'!O24</f>
         <v>560572</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="2">
         <f>'OLD Data'!P24</f>
         <v>45676</v>
       </c>
@@ -6995,7 +7024,7 @@
         <f>'OLD Data'!O25</f>
         <v>411206</v>
       </c>
-      <c r="H25" s="3">
+      <c r="H25" s="2">
         <f>'OLD Data'!P25</f>
         <v>45681</v>
       </c>
@@ -7037,7 +7066,7 @@
         <f>'OLD Data'!O26</f>
         <v>500025</v>
       </c>
-      <c r="H26" s="3">
+      <c r="H26" s="2">
         <f>'OLD Data'!P26</f>
         <v>45658</v>
       </c>
@@ -7079,7 +7108,7 @@
         <f>'OLD Data'!O27</f>
         <v>500026</v>
       </c>
-      <c r="H27" s="3">
+      <c r="H27" s="2">
         <f>'OLD Data'!P27</f>
         <v>45659</v>
       </c>
@@ -7121,7 +7150,7 @@
         <f>'OLD Data'!O28</f>
         <v>500027</v>
       </c>
-      <c r="H28" s="3">
+      <c r="H28" s="2">
         <f>'OLD Data'!P28</f>
         <v>45660</v>
       </c>
@@ -7163,7 +7192,7 @@
         <f>'OLD Data'!O29</f>
         <v>500028</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29" s="2">
         <f>'OLD Data'!P29</f>
         <v>45661</v>
       </c>
@@ -7205,7 +7234,7 @@
         <f>'OLD Data'!O30</f>
         <v>500029</v>
       </c>
-      <c r="H30" s="3">
+      <c r="H30" s="2">
         <f>'OLD Data'!P30</f>
         <v>45662</v>
       </c>
@@ -7247,7 +7276,7 @@
         <f>'OLD Data'!O31</f>
         <v>500030</v>
       </c>
-      <c r="H31" s="3">
+      <c r="H31" s="2">
         <f>'OLD Data'!P31</f>
         <v>45663</v>
       </c>
@@ -7289,7 +7318,7 @@
         <f>'OLD Data'!O32</f>
         <v>500031</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="2">
         <f>'OLD Data'!P32</f>
         <v>45664</v>
       </c>
@@ -7331,7 +7360,7 @@
         <f>'OLD Data'!O33</f>
         <v>500032</v>
       </c>
-      <c r="H33" s="3">
+      <c r="H33" s="2">
         <f>'OLD Data'!P33</f>
         <v>45665</v>
       </c>
@@ -7373,7 +7402,7 @@
         <f>'OLD Data'!O34</f>
         <v>500033</v>
       </c>
-      <c r="H34" s="3">
+      <c r="H34" s="2">
         <f>'OLD Data'!P34</f>
         <v>45666</v>
       </c>
@@ -7415,7 +7444,7 @@
         <f>'OLD Data'!O35</f>
         <v>500034</v>
       </c>
-      <c r="H35" s="3">
+      <c r="H35" s="2">
         <f>'OLD Data'!P35</f>
         <v>45667</v>
       </c>
@@ -7457,7 +7486,7 @@
         <f>'OLD Data'!O36</f>
         <v>500035</v>
       </c>
-      <c r="H36" s="3">
+      <c r="H36" s="2">
         <f>'OLD Data'!P36</f>
         <v>45668</v>
       </c>
@@ -7499,7 +7528,7 @@
         <f>'OLD Data'!O37</f>
         <v>500036</v>
       </c>
-      <c r="H37" s="3">
+      <c r="H37" s="2">
         <f>'OLD Data'!P37</f>
         <v>45669</v>
       </c>
@@ -7541,7 +7570,7 @@
         <f>'OLD Data'!O38</f>
         <v>500037</v>
       </c>
-      <c r="H38" s="3">
+      <c r="H38" s="2">
         <f>'OLD Data'!P38</f>
         <v>45670</v>
       </c>
@@ -7583,7 +7612,7 @@
         <f>'OLD Data'!O39</f>
         <v>500038</v>
       </c>
-      <c r="H39" s="3">
+      <c r="H39" s="2">
         <f>'OLD Data'!P39</f>
         <v>45671</v>
       </c>
@@ -7625,7 +7654,7 @@
         <f>'OLD Data'!O40</f>
         <v>500039</v>
       </c>
-      <c r="H40" s="3">
+      <c r="H40" s="2">
         <f>'OLD Data'!P40</f>
         <v>45672</v>
       </c>
@@ -7667,7 +7696,7 @@
         <f>'OLD Data'!O41</f>
         <v>500040</v>
       </c>
-      <c r="H41" s="3">
+      <c r="H41" s="2">
         <f>'OLD Data'!P41</f>
         <v>45673</v>
       </c>
@@ -7709,7 +7738,7 @@
         <f>'OLD Data'!O42</f>
         <v>500041</v>
       </c>
-      <c r="H42" s="3">
+      <c r="H42" s="2">
         <f>'OLD Data'!P42</f>
         <v>45674</v>
       </c>
@@ -7751,7 +7780,7 @@
         <f>'OLD Data'!O43</f>
         <v>500042</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="2">
         <f>'OLD Data'!P43</f>
         <v>45675</v>
       </c>
@@ -7793,7 +7822,7 @@
         <f>'OLD Data'!O44</f>
         <v>500043</v>
       </c>
-      <c r="H44" s="3">
+      <c r="H44" s="2">
         <f>'OLD Data'!P44</f>
         <v>45676</v>
       </c>
@@ -7835,7 +7864,7 @@
         <f>'OLD Data'!O45</f>
         <v>500044</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="2">
         <f>'OLD Data'!P45</f>
         <v>45677</v>
       </c>
@@ -7877,7 +7906,7 @@
         <f>'OLD Data'!O46</f>
         <v>500045</v>
       </c>
-      <c r="H46" s="3">
+      <c r="H46" s="2">
         <f>'OLD Data'!P46</f>
         <v>45678</v>
       </c>
@@ -7919,7 +7948,7 @@
         <f>'OLD Data'!O47</f>
         <v>500046</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="2">
         <f>'OLD Data'!P47</f>
         <v>45679</v>
       </c>
@@ -7961,7 +7990,7 @@
         <f>'OLD Data'!O48</f>
         <v>500047</v>
       </c>
-      <c r="H48" s="3">
+      <c r="H48" s="2">
         <f>'OLD Data'!P48</f>
         <v>45680</v>
       </c>
@@ -8003,7 +8032,7 @@
         <f>'OLD Data'!O49</f>
         <v>500048</v>
       </c>
-      <c r="H49" s="3">
+      <c r="H49" s="2">
         <f>'OLD Data'!P49</f>
         <v>45681</v>
       </c>
@@ -8045,7 +8074,7 @@
         <f>'OLD Data'!O50</f>
         <v>500049</v>
       </c>
-      <c r="H50" s="3">
+      <c r="H50" s="2">
         <f>'OLD Data'!P50</f>
         <v>45682</v>
       </c>
@@ -8087,7 +8116,7 @@
         <f>'OLD Data'!O51</f>
         <v>500050</v>
       </c>
-      <c r="H51" s="3">
+      <c r="H51" s="2">
         <f>'OLD Data'!P51</f>
         <v>45683</v>
       </c>
@@ -8106,12 +8135,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db0ba53e-1dc5-4ed7-8881-11f125da468b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4d07b3ec-8c3b-4de2-8537-6a594c5b2a50" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8344,20 +8375,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db0ba53e-1dc5-4ed7-8881-11f125da468b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4d07b3ec-8c3b-4de2-8537-6a594c5b2a50" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E2ABD53-257B-47D7-9A4D-18762EB38D1A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBF941B3-D6ED-4D86-8C82-E89A77206751}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="db0ba53e-1dc5-4ed7-8881-11f125da468b"/>
+    <ds:schemaRef ds:uri="4d07b3ec-8c3b-4de2-8537-6a594c5b2a50"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8382,12 +8414,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBF941B3-D6ED-4D86-8C82-E89A77206751}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E2ABD53-257B-47D7-9A4D-18762EB38D1A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="db0ba53e-1dc5-4ed7-8881-11f125da468b"/>
-    <ds:schemaRef ds:uri="4d07b3ec-8c3b-4de2-8537-6a594c5b2a50"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>